--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 21.10.2026, 19:14:00 · ceny netto w zł · szablon NK41</t>
+    <t>Wygenerowano 21.10.2026, 19:25:59 · ceny netto w zł · szablon NK41</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
@@ -17,10 +17,10 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="B42" authorId="0">
+    <comment ref="B43" authorId="0">
       <text/>
     </comment>
-    <comment ref="B43" authorId="0">
+    <comment ref="B44" authorId="0">
       <text/>
     </comment>
   </commentList>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="151">
   <si>
     <t>KALKULACJA NK41</t>
   </si>
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 21.10.2026, 19:25:59 · ceny netto w zł · szablon NK41</t>
+    <t>Wygenerowano 22.10.2026, 08:15:57 · ceny netto w zł · szablon NK41</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>
@@ -54,13 +54,13 @@
     <t>Próg opłacalności · zysk 0%</t>
   </si>
   <si>
-    <t>10 923 zł / MP · 2526 € / MP</t>
-  </si>
-  <si>
-    <t>rabat −19 369 zł (−3,85%)</t>
-  </si>
-  <si>
-    <t>maks. rabat −80 126 zł (−15,95%)</t>
+    <t>10 909 zł / MP · 2522 € / MP</t>
+  </si>
+  <si>
+    <t>rabat −19 323 zł (−3,85%)</t>
+  </si>
+  <si>
+    <t>maks. rabat −79 949 zł (−15,93%)</t>
   </si>
   <si>
     <t>Pole do negocjacji: o ile można zejść z ceny (2000 kg)</t>
@@ -102,7 +102,7 @@
     <t>Prześwit</t>
   </si>
   <si>
-    <t>23× NKPXL</t>
+    <t>23× NK41</t>
   </si>
   <si>
     <t>280 cm</t>
@@ -168,6 +168,15 @@
     <t>przy zysku 11%</t>
   </si>
   <si>
+    <t>Wariant 2500 kg</t>
+  </si>
+  <si>
+    <t>nie wpisano ceny dla zwiększonego udźwigu</t>
+  </si>
+  <si>
+    <t>–</t>
+  </si>
+  <si>
     <t>Słupki e-ładowarek 3,7 kW</t>
   </si>
   <si>
@@ -276,6 +285,9 @@
     <t>348 801 zł</t>
   </si>
   <si>
+    <t>Suma 2500 kg (+0%)</t>
+  </si>
+  <si>
     <t>Montaż, narzuty i cena</t>
   </si>
   <si>
@@ -384,13 +396,13 @@
     <t>KOB</t>
   </si>
   <si>
-    <t>0,52% ceny przed podatkiem (486 789 zł)</t>
+    <t>0,5% ceny przed podatkiem (486 203 zł)</t>
   </si>
   <si>
     <t>GDW</t>
   </si>
   <si>
-    <t>2,59% ceny przed podatkiem</t>
+    <t>2,5% ceny przed podatkiem</t>
   </si>
   <si>
     <t>Zysk 14%</t>
@@ -402,7 +414,7 @@
     <t>Zysk z narzutem (zysk + GDW)</t>
   </si>
   <si>
-    <t>zysk 14% + GDW 2,59%</t>
+    <t>zysk 14% + GDW 2,5%</t>
   </si>
   <si>
     <t>Podatek</t>
@@ -432,34 +444,43 @@
     <t/>
   </si>
   <si>
+    <t>1420 PLN</t>
+  </si>
+  <si>
+    <t>Hotel / doba / osoba</t>
+  </si>
+  <si>
+    <t>780 EUR</t>
+  </si>
+  <si>
+    <t>Dieta dzienna</t>
+  </si>
+  <si>
+    <t>1400 PLN</t>
+  </si>
+  <si>
+    <t>Typy urządzeń (cena, MP, osobodni)</t>
+  </si>
+  <si>
+    <t>500 PLN</t>
+  </si>
+  <si>
+    <t>Platformy NK41</t>
+  </si>
+  <si>
+    <t>12000 PLN/szt., 2 MP, 2.2 osd</t>
+  </si>
+  <si>
+    <t>Wariant 2</t>
+  </si>
+  <si>
     <t>Pozycje kosztowe</t>
   </si>
   <si>
-    <t>Hotel / doba / osoba</t>
-  </si>
-  <si>
-    <t>1420 PLN</t>
-  </si>
-  <si>
-    <t>Dieta dzienna</t>
-  </si>
-  <si>
-    <t>780 EUR</t>
-  </si>
-  <si>
-    <t>Typy urządzeń (cena, MP, osobodni)</t>
-  </si>
-  <si>
-    <t>1400 PLN</t>
-  </si>
-  <si>
-    <t>Platformy NK41</t>
-  </si>
-  <si>
-    <t>12000 PLN/szt., 2 MP, 2.2 osd</t>
-  </si>
-  <si>
-    <t>500 PLN</t>
+    <t>2500 kg</t>
+  </si>
+  <si>
+    <t>0 PLN/szt.</t>
   </si>
 </sst>
 </file>
@@ -933,10 +954,10 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="171" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1278,7 +1299,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1337,15 +1358,15 @@
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
-        <v>502467.51701596996</v>
+        <v>501809.5481100001</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7">
-        <v>483098.8777255402</v>
+        <v>482486.38289686054</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="8">
-        <v>422341.1819259433</v>
+        <v>421860.7820735052</v>
       </c>
       <c r="F6" s="8"/>
     </row>
@@ -1398,7 +1419,7 @@
         <v>0.14</v>
       </c>
       <c r="B11" s="14">
-        <v>502467.51701596996</v>
+        <v>501809.5481100001</v>
       </c>
       <c r="C11" s="14">
         <v>0</v>
@@ -1407,10 +1428,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="14">
-        <v>80733.98765965021</v>
+        <v>80223.44550000002</v>
       </c>
       <c r="F11" s="14">
-        <v>10923.206891651522</v>
+        <v>10908.90321978261</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1418,19 +1439,19 @@
         <v>0.12</v>
       </c>
       <c r="B12" s="17">
-        <v>489403.00099674804</v>
+        <v>488775.8837309412</v>
       </c>
       <c r="C12" s="17">
-        <v>-13064.51601922192</v>
+        <v>-13033.664379058871</v>
       </c>
       <c r="D12" s="18">
-        <v>-0.026000717612172906</v>
+        <v>-0.025973328782101616</v>
       </c>
       <c r="E12" s="17">
-        <v>69325.69016472322</v>
+        <v>68840.5822882353</v>
       </c>
       <c r="F12" s="17">
-        <v>10639.195673842349</v>
+        <v>10625.56268980307</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1438,19 +1459,19 @@
         <v>0.11</v>
       </c>
       <c r="B13" s="20">
-        <v>483098.8777255402</v>
+        <v>482486.38289686054</v>
       </c>
       <c r="C13" s="20">
-        <v>-19368.639290429768</v>
+        <v>-19323.165213139553</v>
       </c>
       <c r="D13" s="21">
-        <v>-0.038547047589176146</v>
+        <v>-0.03850696999672031</v>
       </c>
       <c r="E13" s="20">
-        <v>63820.75499400466</v>
+        <v>63347.68899418606</v>
       </c>
       <c r="F13" s="20">
-        <v>10502.149515772613</v>
+        <v>10488.834410801315</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1458,19 +1479,19 @@
         <v>0.1</v>
       </c>
       <c r="B14" s="23">
-        <v>476939.8435975133</v>
+        <v>476341.4682888506</v>
       </c>
       <c r="C14" s="23">
-        <v>-25527.67341845669</v>
+        <v>-25468.07982114947</v>
       </c>
       <c r="D14" s="24">
-        <v>-0.05080462428707673</v>
+        <v>-0.05075248152824444</v>
       </c>
       <c r="E14" s="23">
-        <v>58442.515684522456</v>
+        <v>57981.06910919541</v>
       </c>
       <c r="F14" s="23">
-        <v>10368.257469511158</v>
+        <v>10355.249310627187</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1478,19 +1499,19 @@
         <v>0.08</v>
       </c>
       <c r="B15" s="23">
-        <v>465037.4581847458</v>
+        <v>464465.9029789888</v>
       </c>
       <c r="C15" s="23">
-        <v>-37430.05883122416</v>
+        <v>-37343.64513101132</v>
       </c>
       <c r="D15" s="24">
-        <v>-0.07449249466614678</v>
+        <v>-0.07441796448804384</v>
       </c>
       <c r="E15" s="23">
-        <v>48049.022845725536</v>
+        <v>47609.623938202254</v>
       </c>
       <c r="F15" s="23">
-        <v>10109.509960537953</v>
+        <v>10097.08484736932</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1498,19 +1519,19 @@
         <v>0.06</v>
       </c>
       <c r="B16" s="23">
-        <v>453658.8301058735</v>
+        <v>453112.3405398901</v>
       </c>
       <c r="C16" s="23">
-        <v>-48808.68691009644</v>
+        <v>-48697.20757010998</v>
       </c>
       <c r="D16" s="24">
-        <v>-0.0971379945114843</v>
+        <v>-0.09704320643862126</v>
       </c>
       <c r="E16" s="23">
-        <v>38112.88942777778</v>
+        <v>37694.066467032964</v>
       </c>
       <c r="F16" s="23">
-        <v>9862.148480562468</v>
+        <v>9850.268272606307</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1518,19 +1539,19 @@
         <v>0.04</v>
       </c>
       <c r="B17" s="23">
-        <v>442770.13219186116</v>
+        <v>442247.1033669893</v>
       </c>
       <c r="C17" s="23">
-        <v>-59697.3848241088</v>
+        <v>-59562.4447430108</v>
       </c>
       <c r="D17" s="24">
-        <v>-0.11880844592429929</v>
+        <v>-0.11869531970315221</v>
       </c>
       <c r="E17" s="23">
-        <v>28604.576609095806</v>
+        <v>28204.98458602151</v>
       </c>
       <c r="F17" s="23">
-        <v>9625.437656344808</v>
+        <v>9614.067464499767</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1538,19 +1559,19 @@
         <v>0.02</v>
       </c>
       <c r="B18" s="23">
-        <v>432340.38887907175</v>
+        <v>431839.3498645264</v>
       </c>
       <c r="C18" s="23">
-        <v>-70127.12813689822</v>
+        <v>-69970.19824547367</v>
       </c>
       <c r="D18" s="24">
-        <v>-0.13956549580232738</v>
+        <v>-0.1394357650407555</v>
       </c>
       <c r="E18" s="23">
-        <v>19497.03566896734</v>
+        <v>19115.442994736844</v>
       </c>
       <c r="F18" s="23">
-        <v>9398.704106066778</v>
+        <v>9387.811953576662</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1558,19 +1579,19 @@
         <v>0</v>
       </c>
       <c r="B19" s="26">
-        <v>422341.1819259433</v>
+        <v>421860.7820735052</v>
       </c>
       <c r="C19" s="26">
-        <v>-80126.33509002667</v>
+        <v>-79948.76603649487</v>
       </c>
       <c r="D19" s="27">
-        <v>-0.15946570151614398</v>
+        <v>-0.15932093428196298</v>
       </c>
       <c r="E19" s="26">
-        <v>10765.451011197112</v>
+        <v>10400.727860824743</v>
       </c>
       <c r="F19" s="26">
-        <v>9181.330041868332</v>
+        <v>9170.88656681533</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1742,105 +1763,109 @@
       </c>
       <c r="C36" s="38"/>
       <c r="D36" s="38"/>
-      <c r="E36" s="39">
-        <v>113348.26902456442</v>
-      </c>
-      <c r="F36" s="39">
-        <v>108991.05655572063</v>
+      <c r="E36" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="F36" s="39" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C37" s="38"/>
       <c r="D37" s="38"/>
       <c r="E37" s="39">
-        <v>374522.141642176</v>
+        <v>113200.25086602406</v>
       </c>
       <c r="F37" s="39">
-        <v>360009.0081273155</v>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="40" t="s">
-        <v>50</v>
-      </c>
-      <c r="B39" s="40"/>
-      <c r="C39" s="40"/>
-      <c r="D39" s="40" t="s">
+        <v>108853.26834744174</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="E39" s="40"/>
-      <c r="F39" s="40"/>
-    </row>
-    <row r="40" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="41" t="s">
+      <c r="B38" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="B40" s="41"/>
-      <c r="C40" s="41"/>
-      <c r="D40" s="41" t="s">
+      <c r="C38" s="38"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="39">
+        <v>374029.1183359035</v>
+      </c>
+      <c r="F38" s="39">
+        <v>359550.0590451161</v>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="E40" s="41"/>
-      <c r="F40" s="41"/>
-    </row>
-    <row r="41" ht="17" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="42" t="s">
+      <c r="B40" s="40"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="B41" s="42"/>
-      <c r="C41" s="42"/>
-      <c r="D41" s="42" t="s">
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
+    </row>
+    <row r="41" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="E41" s="42"/>
-      <c r="F41" s="42"/>
-    </row>
-    <row r="42" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="43" t="s">
+      <c r="B41" s="41"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="B42" s="43"/>
-      <c r="C42" s="43"/>
-      <c r="D42" s="43" t="s">
+      <c r="E41" s="41"/>
+      <c r="F41" s="41"/>
+    </row>
+    <row r="42" ht="17" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-    </row>
-    <row r="44" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="10" t="s">
+      <c r="B42" s="42"/>
+      <c r="C42" s="42"/>
+      <c r="D42" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="44" t="s">
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+    </row>
+    <row r="43" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="B45" s="45" t="s">
+      <c r="B43" s="43"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="C45" s="45"/>
-      <c r="D45" s="45"/>
-      <c r="E45" s="45"/>
-      <c r="F45" s="45"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="43"/>
+    </row>
+    <row r="45" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" s="10"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="44" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B46" s="45" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C46" s="45"/>
       <c r="D46" s="45"/>
@@ -1849,10 +1874,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="44" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B47" s="45" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C47" s="45"/>
       <c r="D47" s="45"/>
@@ -1861,18 +1886,30 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="44" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B48" s="45" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C48" s="45"/>
       <c r="D48" s="45"/>
       <c r="E48" s="45"/>
       <c r="F48" s="45"/>
     </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="B49" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="C49" s="45"/>
+      <c r="D49" s="45"/>
+      <c r="E49" s="45"/>
+      <c r="F49" s="45"/>
+    </row>
   </sheetData>
-  <mergeCells count="54">
+  <mergeCells count="55">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A2:D2"/>
@@ -1914,19 +1951,20 @@
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="B37:D37"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="B38:D38"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="D41:F41"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="D42:F42"/>
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="A45:F45"/>
     <mergeCell ref="B46:F46"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B48:F48"/>
+    <mergeCell ref="B49:F49"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.25" footer="0.25"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="80" fitToWidth="1" fitToHeight="1"/>
@@ -1938,7 +1976,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1947,7 +1985,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="46" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B1" s="46"/>
       <c r="C1" s="46"/>
@@ -1956,7 +1994,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1965,7 +2003,7 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -1974,10 +2012,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="44" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B5" s="45" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C5" s="45"/>
       <c r="D5" s="45"/>
@@ -1985,10 +2023,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="44" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B6" s="45" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C6" s="45"/>
       <c r="D6" s="45"/>
@@ -1996,10 +2034,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="44" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B7" s="45" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C7" s="45"/>
       <c r="D7" s="45"/>
@@ -2007,10 +2045,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="44" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B8" s="45" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C8" s="45"/>
       <c r="D8" s="45"/>
@@ -2018,10 +2056,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="44" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B9" s="45" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C9" s="45"/>
       <c r="D9" s="45"/>
@@ -2029,444 +2067,470 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B10" s="45" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C10" s="45"/>
       <c r="D10" s="45"/>
       <c r="E10" s="45"/>
     </row>
-    <row r="12" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-    </row>
-    <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="47" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13" s="47" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="48" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="49" t="s">
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="50" t="s">
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="51">
+      <c r="B14" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="48" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="49" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="50"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="51">
         <v>50.6</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="52" t="s">
-        <v>88</v>
-      </c>
-      <c r="B15" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="54">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" s="53" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="54">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="49" t="s">
-        <v>90</v>
-      </c>
-      <c r="B16" s="50" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="51">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="49" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" s="50" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="50"/>
+      <c r="D17" s="50"/>
+      <c r="E17" s="51">
         <v>19.6338</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="B17" s="53" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" s="53"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="54">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="52" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" s="53" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="54">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="49" t="s">
-        <v>94</v>
-      </c>
-      <c r="B18" s="50" t="s">
-        <v>95</v>
-      </c>
-      <c r="C18" s="50"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="55">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="55">
         <v>3640</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="52" t="s">
-        <v>96</v>
-      </c>
-      <c r="B19" s="53" t="s">
-        <v>97</v>
-      </c>
-      <c r="C19" s="53"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="54">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="B20" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="54">
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="49" t="s">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="50" t="s">
-        <v>98</v>
-      </c>
-      <c r="C20" s="50"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="56">
+      <c r="B21" s="50" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21" s="50"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="56">
         <v>348801</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="52" t="s">
-        <v>99</v>
-      </c>
-      <c r="B21" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="57">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="53" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="57">
         <v>4113.2</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="49" t="s">
-        <v>101</v>
-      </c>
-      <c r="B22" s="50" t="s">
-        <v>102</v>
-      </c>
-      <c r="C22" s="50"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="56">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="C23" s="50"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="56">
         <v>9880</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="52" t="s">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="53" t="s">
-        <v>103</v>
-      </c>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="57">
+      <c r="B24" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="57">
         <v>3200</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="49" t="s">
-        <v>104</v>
-      </c>
-      <c r="B24" s="50" t="s">
-        <v>105</v>
-      </c>
-      <c r="C24" s="50"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="56">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="49" t="s">
+        <v>108</v>
+      </c>
+      <c r="B25" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" s="50"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="56">
         <v>4800</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="52" t="s">
-        <v>106</v>
-      </c>
-      <c r="B25" s="53" t="s">
-        <v>107</v>
-      </c>
-      <c r="C25" s="53"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="57">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="B26" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="57">
         <v>1500</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="49" t="s">
-        <v>108</v>
-      </c>
-      <c r="B26" s="50" t="s">
-        <v>109</v>
-      </c>
-      <c r="C26" s="50"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="56">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="49" t="s">
+        <v>112</v>
+      </c>
+      <c r="B27" s="50" t="s">
+        <v>113</v>
+      </c>
+      <c r="C27" s="50"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="56">
         <v>800</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="52" t="s">
-        <v>110</v>
-      </c>
-      <c r="B27" s="53" t="s">
-        <v>111</v>
-      </c>
-      <c r="C27" s="53"/>
-      <c r="D27" s="53"/>
-      <c r="E27" s="57">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="B28" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="C28" s="53"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="57">
         <v>7053.52</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="49" t="s">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="50" t="s">
-        <v>112</v>
-      </c>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="56">
+      <c r="B29" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="56">
         <v>20240</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="52" t="s">
-        <v>113</v>
-      </c>
-      <c r="B29" s="53" t="s">
-        <v>114</v>
-      </c>
-      <c r="C29" s="53"/>
-      <c r="D29" s="53"/>
-      <c r="E29" s="57">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="52" t="s">
+        <v>117</v>
+      </c>
+      <c r="B30" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="C30" s="53"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="57">
         <v>3160.521</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="58" t="s">
-        <v>115</v>
-      </c>
-      <c r="B30" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="C30" s="59"/>
-      <c r="D30" s="59"/>
-      <c r="E30" s="60">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="C31" s="59"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="60">
         <v>403548.24100000004</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="52" t="s">
-        <v>117</v>
-      </c>
-      <c r="B31" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="C31" s="53"/>
-      <c r="D31" s="53"/>
-      <c r="E31" s="57">
-        <v>2506.9643439686374</v>
-      </c>
-    </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="49" t="s">
-        <v>119</v>
-      </c>
-      <c r="B32" s="50" t="s">
-        <v>120</v>
-      </c>
-      <c r="C32" s="50"/>
-      <c r="D32" s="50"/>
-      <c r="E32" s="56">
-        <v>12583.500639143549</v>
+      <c r="A32" s="52" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="C32" s="53"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="57">
+        <v>2431.0135000000005</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="52" t="s">
-        <v>121</v>
-      </c>
-      <c r="B33" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="C33" s="53"/>
-      <c r="D33" s="53"/>
-      <c r="E33" s="57">
-        <v>68150.48702050665</v>
+      <c r="A33" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="B33" s="50" t="s">
+        <v>124</v>
+      </c>
+      <c r="C33" s="50"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="56">
+        <v>12155.067500000003</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="49" t="s">
-        <v>123</v>
-      </c>
-      <c r="B34" s="50" t="s">
-        <v>124</v>
-      </c>
-      <c r="C34" s="50"/>
-      <c r="D34" s="50"/>
-      <c r="E34" s="56">
-        <v>80733.98765965021</v>
+      <c r="A34" s="52" t="s">
+        <v>125</v>
+      </c>
+      <c r="B34" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="C34" s="53"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="57">
+        <v>68068.37800000001</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="52" t="s">
-        <v>125</v>
-      </c>
-      <c r="B35" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="C35" s="53"/>
-      <c r="D35" s="53"/>
-      <c r="E35" s="57">
-        <v>15678.324012351031</v>
+      <c r="A35" s="49" t="s">
+        <v>127</v>
+      </c>
+      <c r="B35" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="C35" s="50"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="56">
+        <v>80223.44550000002</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="58" t="s">
-        <v>127</v>
-      </c>
-      <c r="B36" s="59" t="s">
-        <v>128</v>
-      </c>
-      <c r="C36" s="59"/>
-      <c r="D36" s="59"/>
-      <c r="E36" s="60">
-        <v>502467.51701596996</v>
+      <c r="A36" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="B36" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="C36" s="53"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="57">
+        <v>15606.848110000003</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="58" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B37" s="59" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C37" s="59"/>
       <c r="D37" s="59"/>
       <c r="E37" s="60">
-        <v>421733.52935631975</v>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="B38" s="46"/>
-      <c r="C38" s="46"/>
-      <c r="D38" s="46"/>
-      <c r="E38" s="46"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-    </row>
-    <row r="41" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="61" t="s">
+        <v>501809.5481100001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="B38" s="59" t="s">
+        <v>134</v>
+      </c>
+      <c r="C38" s="59"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="60">
+        <v>421586.10261000006</v>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="B39" s="46"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="46"/>
+      <c r="E39" s="46"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+    </row>
+    <row r="42" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="B41" s="62" t="s">
-        <v>133</v>
-      </c>
-      <c r="C41" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="D41" s="61"/>
-      <c r="E41" s="62" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="42" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="63" t="s">
-        <v>135</v>
-      </c>
-      <c r="B42" s="64">
-        <v>130</v>
+      <c r="B42" s="62" t="s">
+        <v>137</v>
       </c>
       <c r="C42" s="63" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D42" s="63"/>
-      <c r="E42" s="65" t="s">
-        <v>136</v>
+      <c r="E42" s="64" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="43" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="63" t="s">
+        <v>139</v>
+      </c>
+      <c r="B43" s="65">
+        <v>130</v>
+      </c>
+      <c r="C43" s="63" t="s">
+        <v>77</v>
+      </c>
+      <c r="D43" s="63"/>
+      <c r="E43" s="64" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="44" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="63" t="s">
+        <v>141</v>
+      </c>
+      <c r="B44" s="65">
+        <v>45</v>
+      </c>
+      <c r="C44" s="63" t="s">
+        <v>79</v>
+      </c>
+      <c r="D44" s="63"/>
+      <c r="E44" s="64" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="45" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="61" t="s">
+        <v>143</v>
+      </c>
+      <c r="B45" s="62" t="s">
         <v>137</v>
       </c>
-      <c r="B43" s="64">
-        <v>45</v>
-      </c>
-      <c r="C43" s="63" t="s">
-        <v>74</v>
-      </c>
-      <c r="D43" s="63"/>
-      <c r="E43" s="65" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="44" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="61" t="s">
-        <v>139</v>
-      </c>
-      <c r="B44" s="62" t="s">
-        <v>133</v>
-      </c>
-      <c r="C44" s="63" t="s">
-        <v>76</v>
-      </c>
-      <c r="D44" s="63"/>
-      <c r="E44" s="65" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="45" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="63" t="s">
-        <v>141</v>
-      </c>
-      <c r="B45" s="65" t="s">
-        <v>142</v>
-      </c>
       <c r="C45" s="63" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D45" s="63"/>
-      <c r="E45" s="65" t="s">
-        <v>143</v>
+      <c r="E45" s="64" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="46" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="63" t="s">
+        <v>145</v>
+      </c>
+      <c r="B46" s="64" t="s">
+        <v>146</v>
+      </c>
+      <c r="C46" s="61" t="s">
+        <v>147</v>
+      </c>
+      <c r="D46" s="61"/>
+      <c r="E46" s="62" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="47" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="61" t="s">
+        <v>148</v>
+      </c>
+      <c r="B47" s="62" t="s">
+        <v>137</v>
+      </c>
+      <c r="C47" s="63" t="s">
+        <v>149</v>
+      </c>
+      <c r="D47" s="63"/>
+      <c r="E47" s="64" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="42">
+  <mergeCells count="44">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A4:E4"/>
@@ -2476,8 +2540,8 @@
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B10:E10"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B16:D16"/>
@@ -2502,13 +2566,15 @@
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="B37:D37"/>
-    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="B38:D38"/>
     <mergeCell ref="A39:E39"/>
-    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="A40:E40"/>
     <mergeCell ref="C42:D42"/>
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.25" footer="0.25"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="82" fitToWidth="1" fitToHeight="1"/>
@@ -2516,7 +2582,7 @@
     <oddFooter>&amp;L&amp;8ul. Leśna 5, Wrocław&amp;R&amp;8Strona &amp;P z &amp;N</oddFooter>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="37" max="16838" man="1"/>
+    <brk id="38" max="16838" man="1"/>
   </rowBreaks>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 22.10.2026, 08:15:57 · ceny netto w zł · szablon NK41</t>
+    <t>Wygenerowano 22.10.2026, 08:47:04 · ceny netto w zł · szablon NK41</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 22.10.2026, 08:47:04 · ceny netto w zł · szablon NK41</t>
+    <t>Wygenerowano 23.10.2026, 05:42:40 · ceny netto w zł · szablon NK41</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 23.10.2026, 05:42:40 · ceny netto w zł · szablon NK41</t>
+    <t>Wygenerowano 23.10.2026, 06:31:44 · ceny netto w zł · szablon NK41</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 23.10.2026, 06:31:44 · ceny netto w zł · szablon NK41</t>
+    <t>Wygenerowano 23.10.2026, 06:32:56 · ceny netto w zł · szablon NK41</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 23.10.2026, 06:32:56 · ceny netto w zł · szablon NK41</t>
+    <t>Wygenerowano 27.10.2026, 12:24:44 · ceny netto w zł · szablon NK41</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 27.10.2026, 12:24:44 · ceny netto w zł · szablon NK41</t>
+    <t>Wygenerowano 27.10.2026, 14:03:05 · ceny netto w zł · szablon NK41</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 27.10.2026, 14:03:05 · ceny netto w zł · szablon NK41</t>
+    <t>Wygenerowano 27.10.2026, 14:04:45 · ceny netto w zł · szablon NK41</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>
@@ -105,7 +105,7 @@
     <t>23× NK41</t>
   </si>
   <si>
-    <t>280 cm</t>
+    <t>P 280 cm</t>
   </si>
   <si>
     <t>Razem</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="153">
   <si>
     <t>KALKULACJA NK41</t>
   </si>
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 27.10.2026, 14:04:45 · ceny netto w zł · szablon NK41</t>
+    <t>Wygenerowano 27.10.2026, 14:13:52 · ceny netto w zł · szablon NK41</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>
@@ -132,6 +132,15 @@
     <t>400 cm</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>KOB / GDW</t>
+  </si>
+  <si>
+    <t>0,5% / 2,5%</t>
+  </si>
+  <si>
     <t>Opis wariantu</t>
   </si>
   <si>
@@ -439,9 +448,6 @@
   </si>
   <si>
     <t>Pomarańczowe = zmienione względem domyślnego NK38</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>1420 PLN</t>
@@ -1299,7 +1305,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1698,198 +1704,198 @@
       <c r="E29" s="32"/>
       <c r="F29" s="32"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="33" t="s">
+    <row r="30" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="34" t="s">
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="35" t="s">
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+    </row>
+    <row r="31" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="32"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="35"/>
-      <c r="C32" s="35" t="s">
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35" t="s">
+      <c r="B33" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="F32" s="35"/>
-    </row>
-    <row r="33" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="36" t="s">
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="36"/>
-      <c r="C33" s="36" t="s">
+      <c r="B34" s="35"/>
+      <c r="C34" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="36"/>
-      <c r="E33" s="36" t="s">
+      <c r="D34" s="35"/>
+      <c r="E34" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="F33" s="36"/>
-    </row>
-    <row r="35" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
+      <c r="F34" s="35"/>
+    </row>
+    <row r="35" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="36"/>
+      <c r="C35" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="12" t="s">
+      <c r="D35" s="36"/>
+      <c r="E35" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="F35" s="12" t="s">
+      <c r="F35" s="36"/>
+    </row>
+    <row r="37" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="11" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="37" t="s">
+      <c r="B37" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B36" s="38" t="s">
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="39" t="s">
+      <c r="F37" s="12" t="s">
         <v>48</v>
-      </c>
-      <c r="F36" s="39" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="B37" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="39">
-        <v>113200.25086602406</v>
-      </c>
-      <c r="F37" s="39">
-        <v>108853.26834744174</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="37" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C38" s="38"/>
       <c r="D38" s="38"/>
-      <c r="E38" s="39">
+      <c r="E38" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="F38" s="39" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" s="38"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="39">
+        <v>113200.25086602406</v>
+      </c>
+      <c r="F39" s="39">
+        <v>108853.26834744174</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="B40" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" s="38"/>
+      <c r="D40" s="38"/>
+      <c r="E40" s="39">
         <v>374029.1183359035</v>
       </c>
-      <c r="F38" s="39">
+      <c r="F40" s="39">
         <v>359550.0590451161</v>
       </c>
     </row>
-    <row r="40" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="B40" s="40"/>
-      <c r="C40" s="40"/>
-      <c r="D40" s="40" t="s">
-        <v>54</v>
-      </c>
-      <c r="E40" s="40"/>
-      <c r="F40" s="40"/>
-    </row>
-    <row r="41" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="B41" s="41"/>
-      <c r="C41" s="41"/>
-      <c r="D41" s="41" t="s">
+    <row r="42" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="E41" s="41"/>
-      <c r="F41" s="41"/>
-    </row>
-    <row r="42" ht="17" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="42" t="s">
+      <c r="B42" s="40"/>
+      <c r="C42" s="40"/>
+      <c r="D42" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="B42" s="42"/>
-      <c r="C42" s="42"/>
-      <c r="D42" s="42" t="s">
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
+    </row>
+    <row r="43" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-    </row>
-    <row r="43" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="43" t="s">
+      <c r="B43" s="41"/>
+      <c r="C43" s="41"/>
+      <c r="D43" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="B43" s="43"/>
-      <c r="C43" s="43"/>
-      <c r="D43" s="43" t="s">
+      <c r="E43" s="41"/>
+      <c r="F43" s="41"/>
+    </row>
+    <row r="44" ht="17" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="E43" s="43"/>
-      <c r="F43" s="43"/>
-    </row>
-    <row r="45" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="10" t="s">
+      <c r="B44" s="42"/>
+      <c r="C44" s="42"/>
+      <c r="D44" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="44" t="s">
+      <c r="E44" s="42"/>
+      <c r="F44" s="42"/>
+    </row>
+    <row r="45" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="45" t="s">
+      <c r="B45" s="43"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="C46" s="45"/>
-      <c r="D46" s="45"/>
-      <c r="E46" s="45"/>
-      <c r="F46" s="45"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="44" t="s">
+      <c r="E45" s="43"/>
+      <c r="F45" s="43"/>
+    </row>
+    <row r="47" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B47" s="45" t="s">
-        <v>65</v>
-      </c>
-      <c r="C47" s="45"/>
-      <c r="D47" s="45"/>
-      <c r="E47" s="45"/>
-      <c r="F47" s="45"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="10"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="B48" s="45" t="s">
         <v>66</v>
-      </c>
-      <c r="B48" s="45" t="s">
-        <v>67</v>
       </c>
       <c r="C48" s="45"/>
       <c r="D48" s="45"/>
@@ -1898,18 +1904,42 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="44" t="s">
+        <v>67</v>
+      </c>
+      <c r="B49" s="45" t="s">
         <v>68</v>
-      </c>
-      <c r="B49" s="45" t="s">
-        <v>69</v>
       </c>
       <c r="C49" s="45"/>
       <c r="D49" s="45"/>
       <c r="E49" s="45"/>
       <c r="F49" s="45"/>
     </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="44" t="s">
+        <v>69</v>
+      </c>
+      <c r="B50" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="45"/>
+      <c r="D50" s="45"/>
+      <c r="E50" s="45"/>
+      <c r="F50" s="45"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="B51" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="C51" s="45"/>
+      <c r="D51" s="45"/>
+      <c r="E51" s="45"/>
+      <c r="F51" s="45"/>
+    </row>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="59">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A2:D2"/>
@@ -1941,30 +1971,34 @@
     <mergeCell ref="D28:F28"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="D29:F29"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E35:F35"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="B38:D38"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B40:D40"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="D42:F42"/>
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="D43:F43"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="A47:F47"/>
     <mergeCell ref="B48:F48"/>
     <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B51:F51"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.25" footer="0.25"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="80" fitToWidth="1" fitToHeight="1"/>
@@ -1985,7 +2019,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="46" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B1" s="46"/>
       <c r="C1" s="46"/>
@@ -1994,7 +2028,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -2003,7 +2037,7 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -2012,10 +2046,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="44" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B5" s="45" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C5" s="45"/>
       <c r="D5" s="45"/>
@@ -2023,10 +2057,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="44" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B6" s="45" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C6" s="45"/>
       <c r="D6" s="45"/>
@@ -2034,10 +2068,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="44" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B7" s="45" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C7" s="45"/>
       <c r="D7" s="45"/>
@@ -2045,10 +2079,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="44" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B8" s="45" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C8" s="45"/>
       <c r="D8" s="45"/>
@@ -2056,10 +2090,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="44" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B9" s="45" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C9" s="45"/>
       <c r="D9" s="45"/>
@@ -2067,10 +2101,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B10" s="45" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C10" s="45"/>
       <c r="D10" s="45"/>
@@ -2078,10 +2112,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="44" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B11" s="45" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C11" s="45"/>
       <c r="D11" s="45"/>
@@ -2089,7 +2123,7 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -2098,23 +2132,23 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="47" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C14" s="47"/>
       <c r="D14" s="47"/>
       <c r="E14" s="48" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="49" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B15" s="50" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C15" s="50"/>
       <c r="D15" s="50"/>
@@ -2124,10 +2158,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="52" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B16" s="53" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C16" s="53"/>
       <c r="D16" s="53"/>
@@ -2137,10 +2171,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="49" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B17" s="50" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C17" s="50"/>
       <c r="D17" s="50"/>
@@ -2150,10 +2184,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="52" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B18" s="53" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C18" s="53"/>
       <c r="D18" s="53"/>
@@ -2163,10 +2197,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="49" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B19" s="50" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C19" s="50"/>
       <c r="D19" s="50"/>
@@ -2176,10 +2210,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="52" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B20" s="53" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C20" s="53"/>
       <c r="D20" s="53"/>
@@ -2192,7 +2226,7 @@
         <v>22</v>
       </c>
       <c r="B21" s="50" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C21" s="50"/>
       <c r="D21" s="50"/>
@@ -2202,10 +2236,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="52" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B22" s="53" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C22" s="53"/>
       <c r="D22" s="53"/>
@@ -2215,10 +2249,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="49" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B23" s="50" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C23" s="50"/>
       <c r="D23" s="50"/>
@@ -2228,10 +2262,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="52" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B24" s="53" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C24" s="53"/>
       <c r="D24" s="53"/>
@@ -2241,10 +2275,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="49" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B25" s="50" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C25" s="50"/>
       <c r="D25" s="50"/>
@@ -2254,10 +2288,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="52" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B26" s="53" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C26" s="53"/>
       <c r="D26" s="53"/>
@@ -2267,10 +2301,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="49" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B27" s="50" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C27" s="50"/>
       <c r="D27" s="50"/>
@@ -2280,10 +2314,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="52" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B28" s="53" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C28" s="53"/>
       <c r="D28" s="53"/>
@@ -2293,10 +2327,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="49" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B29" s="50" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C29" s="50"/>
       <c r="D29" s="50"/>
@@ -2306,10 +2340,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="52" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B30" s="53" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C30" s="53"/>
       <c r="D30" s="53"/>
@@ -2319,10 +2353,10 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="58" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B31" s="59" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C31" s="59"/>
       <c r="D31" s="59"/>
@@ -2332,10 +2366,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="52" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B32" s="53" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C32" s="53"/>
       <c r="D32" s="53"/>
@@ -2345,10 +2379,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="49" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B33" s="50" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C33" s="50"/>
       <c r="D33" s="50"/>
@@ -2358,10 +2392,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="52" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B34" s="53" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C34" s="53"/>
       <c r="D34" s="53"/>
@@ -2371,10 +2405,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="49" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B35" s="50" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C35" s="50"/>
       <c r="D35" s="50"/>
@@ -2384,10 +2418,10 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="52" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B36" s="53" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C36" s="53"/>
       <c r="D36" s="53"/>
@@ -2397,10 +2431,10 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="58" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B37" s="59" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C37" s="59"/>
       <c r="D37" s="59"/>
@@ -2410,10 +2444,10 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="58" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B38" s="59" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C38" s="59"/>
       <c r="D38" s="59"/>
@@ -2423,7 +2457,7 @@
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="46" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B39" s="46"/>
       <c r="C39" s="46"/>
@@ -2432,7 +2466,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -2441,92 +2475,92 @@
     </row>
     <row r="42" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="61" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B42" s="62" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
       <c r="C42" s="63" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D42" s="63"/>
       <c r="E42" s="64" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="63" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B43" s="65">
         <v>130</v>
       </c>
       <c r="C43" s="63" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D43" s="63"/>
       <c r="E43" s="64" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="44" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="63" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B44" s="65">
         <v>45</v>
       </c>
       <c r="C44" s="63" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D44" s="63"/>
       <c r="E44" s="64" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="45" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="61" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B45" s="62" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
       <c r="C45" s="63" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D45" s="63"/>
       <c r="E45" s="64" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="46" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="63" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B46" s="64" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C46" s="61" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D46" s="61"/>
       <c r="E46" s="62" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="61" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B47" s="62" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
       <c r="C47" s="63" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D47" s="63"/>
       <c r="E47" s="64" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 27.10.2026, 14:13:52 · ceny netto w zł · szablon NK41</t>
+    <t>Wygenerowano 27.10.2026, 14:16:58 · ceny netto w zł · szablon NK41</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>
@@ -309,25 +309,25 @@
     <t>Kwota</t>
   </si>
   <si>
-    <t>Osobodni montażu (F50)</t>
+    <t>Osobodni montażu</t>
   </si>
   <si>
     <t>z cennika osobodni na urządzenie + utrudnienia</t>
   </si>
   <si>
-    <t>Tygodnie / dni montażu (B55)</t>
+    <t>Tygodnie / dni montażu</t>
   </si>
   <si>
     <t>tygodniowe wyjazdy ekipy</t>
   </si>
   <si>
-    <t>Osobodni podróży i rozładunku (G59)</t>
+    <t>Osobodni podróży i rozładunku</t>
   </si>
   <si>
     <t>pomiary, odbiory, rozładunek i dojazdy ekipy</t>
   </si>
   <si>
-    <t>Dni pracy ekipy (J39)</t>
+    <t>Dni pracy ekipy</t>
   </si>
   <si>
     <t>(osd montażu + podróży) ÷ 4 os.</t>
@@ -432,7 +432,7 @@
     <t>14% od robocizny (31 254 zł) i zysku z narzutem</t>
   </si>
   <si>
-    <t>Cena kontraktu, zysk 14% (K39)</t>
+    <t>Cena kontraktu, zysk 14%</t>
   </si>
   <si>
     <t>suma ÷ (1 − KOB − GDW − zysk) + podatek</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="151">
   <si>
     <t>KALKULACJA NK41</t>
   </si>
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 27.10.2026, 14:16:58 · ceny netto w zł · szablon NK41</t>
+    <t>Wygenerowano 27.10.2026, 14:20:07 · ceny netto w zł · szablon NK41</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>
@@ -190,12 +190,6 @@
   </si>
   <si>
     <t>46 MP × 1700 zł + montaż</t>
-  </si>
-  <si>
-    <t>Słupki e-ładowarek 22 kW</t>
-  </si>
-  <si>
-    <t>jak 3,7 kW + 4600 zł/MP</t>
   </si>
   <si>
     <t>Konserwacja · wariant 1 · 23 szt.</t>
@@ -1305,7 +1299,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1816,79 +1810,75 @@
         <v>108853.26834744174</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="37" t="s">
+    <row r="41" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="B40" s="38" t="s">
+      <c r="B41" s="40"/>
+      <c r="C41" s="40"/>
+      <c r="D41" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C40" s="38"/>
-      <c r="D40" s="38"/>
-      <c r="E40" s="39">
-        <v>374029.1183359035</v>
-      </c>
-      <c r="F40" s="39">
-        <v>359550.0590451161</v>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="40" t="s">
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+    </row>
+    <row r="42" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="B42" s="40"/>
-      <c r="C42" s="40"/>
-      <c r="D42" s="40" t="s">
+      <c r="B42" s="41"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="E42" s="40"/>
-      <c r="F42" s="40"/>
-    </row>
-    <row r="43" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="41" t="s">
+      <c r="E42" s="41"/>
+      <c r="F42" s="41"/>
+    </row>
+    <row r="43" ht="17" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="B43" s="41"/>
-      <c r="C43" s="41"/>
-      <c r="D43" s="41" t="s">
+      <c r="B43" s="42"/>
+      <c r="C43" s="42"/>
+      <c r="D43" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="E43" s="41"/>
-      <c r="F43" s="41"/>
-    </row>
-    <row r="44" ht="17" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="42" t="s">
+      <c r="E43" s="42"/>
+      <c r="F43" s="42"/>
+    </row>
+    <row r="44" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="B44" s="42"/>
-      <c r="C44" s="42"/>
-      <c r="D44" s="42" t="s">
+      <c r="B44" s="43"/>
+      <c r="C44" s="43"/>
+      <c r="D44" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="E44" s="42"/>
-      <c r="F44" s="42"/>
-    </row>
-    <row r="45" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="43" t="s">
+      <c r="E44" s="43"/>
+      <c r="F44" s="43"/>
+    </row>
+    <row r="46" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="B45" s="43"/>
-      <c r="C45" s="43"/>
-      <c r="D45" s="43" t="s">
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="E45" s="43"/>
-      <c r="F45" s="43"/>
-    </row>
-    <row r="47" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="10" t="s">
+      <c r="B47" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
+      <c r="C47" s="45"/>
+      <c r="D47" s="45"/>
+      <c r="E47" s="45"/>
+      <c r="F47" s="45"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="44" t="s">
@@ -1926,20 +1916,8 @@
       <c r="E50" s="45"/>
       <c r="F50" s="45"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="44" t="s">
-        <v>71</v>
-      </c>
-      <c r="B51" s="45" t="s">
-        <v>72</v>
-      </c>
-      <c r="C51" s="45"/>
-      <c r="D51" s="45"/>
-      <c r="E51" s="45"/>
-      <c r="F51" s="45"/>
-    </row>
   </sheetData>
-  <mergeCells count="59">
+  <mergeCells count="58">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A2:D2"/>
@@ -1985,20 +1963,19 @@
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="D41:F41"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="D42:F42"/>
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="D43:F43"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="D44:F44"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="B47:F47"/>
     <mergeCell ref="B48:F48"/>
     <mergeCell ref="B49:F49"/>
     <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B51:F51"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.25" footer="0.25"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="80" fitToWidth="1" fitToHeight="1"/>
@@ -2019,7 +1996,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="46" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B1" s="46"/>
       <c r="C1" s="46"/>
@@ -2028,7 +2005,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -2037,7 +2014,7 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -2046,10 +2023,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="44" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B5" s="45" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C5" s="45"/>
       <c r="D5" s="45"/>
@@ -2057,10 +2034,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="44" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B6" s="45" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C6" s="45"/>
       <c r="D6" s="45"/>
@@ -2068,10 +2045,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="44" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B7" s="45" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C7" s="45"/>
       <c r="D7" s="45"/>
@@ -2079,10 +2056,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="44" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B8" s="45" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C8" s="45"/>
       <c r="D8" s="45"/>
@@ -2090,10 +2067,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="44" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B9" s="45" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C9" s="45"/>
       <c r="D9" s="45"/>
@@ -2101,10 +2078,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B10" s="45" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C10" s="45"/>
       <c r="D10" s="45"/>
@@ -2112,10 +2089,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="44" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B11" s="45" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C11" s="45"/>
       <c r="D11" s="45"/>
@@ -2123,7 +2100,7 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -2132,23 +2109,23 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="47" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C14" s="47"/>
       <c r="D14" s="47"/>
       <c r="E14" s="48" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="49" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B15" s="50" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C15" s="50"/>
       <c r="D15" s="50"/>
@@ -2158,10 +2135,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="52" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B16" s="53" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C16" s="53"/>
       <c r="D16" s="53"/>
@@ -2171,10 +2148,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B17" s="50" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C17" s="50"/>
       <c r="D17" s="50"/>
@@ -2184,10 +2161,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="52" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B18" s="53" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C18" s="53"/>
       <c r="D18" s="53"/>
@@ -2197,10 +2174,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="49" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B19" s="50" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C19" s="50"/>
       <c r="D19" s="50"/>
@@ -2210,10 +2187,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="52" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B20" s="53" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C20" s="53"/>
       <c r="D20" s="53"/>
@@ -2226,7 +2203,7 @@
         <v>22</v>
       </c>
       <c r="B21" s="50" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C21" s="50"/>
       <c r="D21" s="50"/>
@@ -2236,10 +2213,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="52" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B22" s="53" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C22" s="53"/>
       <c r="D22" s="53"/>
@@ -2249,10 +2226,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="49" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B23" s="50" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C23" s="50"/>
       <c r="D23" s="50"/>
@@ -2265,7 +2242,7 @@
         <v>41</v>
       </c>
       <c r="B24" s="53" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C24" s="53"/>
       <c r="D24" s="53"/>
@@ -2275,10 +2252,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="49" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B25" s="50" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C25" s="50"/>
       <c r="D25" s="50"/>
@@ -2288,10 +2265,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="52" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B26" s="53" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C26" s="53"/>
       <c r="D26" s="53"/>
@@ -2301,10 +2278,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="49" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B27" s="50" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C27" s="50"/>
       <c r="D27" s="50"/>
@@ -2314,10 +2291,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="52" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B28" s="53" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C28" s="53"/>
       <c r="D28" s="53"/>
@@ -2330,7 +2307,7 @@
         <v>40</v>
       </c>
       <c r="B29" s="50" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C29" s="50"/>
       <c r="D29" s="50"/>
@@ -2340,10 +2317,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="52" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B30" s="53" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C30" s="53"/>
       <c r="D30" s="53"/>
@@ -2353,10 +2330,10 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="58" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B31" s="59" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C31" s="59"/>
       <c r="D31" s="59"/>
@@ -2366,10 +2343,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="52" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B32" s="53" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C32" s="53"/>
       <c r="D32" s="53"/>
@@ -2379,10 +2356,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="49" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B33" s="50" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C33" s="50"/>
       <c r="D33" s="50"/>
@@ -2392,10 +2369,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="52" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B34" s="53" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C34" s="53"/>
       <c r="D34" s="53"/>
@@ -2405,10 +2382,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="49" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B35" s="50" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C35" s="50"/>
       <c r="D35" s="50"/>
@@ -2418,10 +2395,10 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="52" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B36" s="53" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C36" s="53"/>
       <c r="D36" s="53"/>
@@ -2431,10 +2408,10 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="58" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B37" s="59" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C37" s="59"/>
       <c r="D37" s="59"/>
@@ -2444,10 +2421,10 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="58" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B38" s="59" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C38" s="59"/>
       <c r="D38" s="59"/>
@@ -2457,7 +2434,7 @@
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="46" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B39" s="46"/>
       <c r="C39" s="46"/>
@@ -2466,7 +2443,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -2481,67 +2458,67 @@
         <v>34</v>
       </c>
       <c r="C42" s="63" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D42" s="63"/>
       <c r="E42" s="64" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="43" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="63" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B43" s="65">
         <v>130</v>
       </c>
       <c r="C43" s="63" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D43" s="63"/>
       <c r="E43" s="64" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="63" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B44" s="65">
         <v>45</v>
       </c>
       <c r="C44" s="63" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D44" s="63"/>
       <c r="E44" s="64" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="61" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B45" s="62" t="s">
         <v>34</v>
       </c>
       <c r="C45" s="63" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D45" s="63"/>
       <c r="E45" s="64" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="46" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="63" t="s">
+        <v>145</v>
+      </c>
+      <c r="B46" s="64" t="s">
+        <v>146</v>
+      </c>
+      <c r="C46" s="61" t="s">
         <v>147</v>
-      </c>
-      <c r="B46" s="64" t="s">
-        <v>148</v>
-      </c>
-      <c r="C46" s="61" t="s">
-        <v>149</v>
       </c>
       <c r="D46" s="61"/>
       <c r="E46" s="62" t="s">
@@ -2550,17 +2527,17 @@
     </row>
     <row r="47" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="61" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B47" s="62" t="s">
         <v>34</v>
       </c>
       <c r="C47" s="63" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D47" s="63"/>
       <c r="E47" s="64" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 27.10.2026, 14:20:07 · ceny netto w zł · szablon NK41</t>
+    <t>Wygenerowano 27.10.2026, 14:21:22 · ceny netto w zł · szablon NK41</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>
@@ -126,7 +126,7 @@
     <t>Długość miejsca postojowego</t>
   </si>
   <si>
-    <t>6 szt.</t>
+    <t>6 szt. (3 kW / 6 kW: nie podano)</t>
   </si>
   <si>
     <t>400 cm</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
@@ -42,7 +42,7 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 27.10.2026, 14:21:22 · ceny netto w zł · szablon NK41</t>
+    <t>Wygenerowano 27.10.2026, 14:28:47 · ceny netto w zł · szablon NK41</t>
   </si>
   <si>
     <t>Cena ofertowa · zysk 14%</t>
@@ -54,13 +54,13 @@
     <t>Próg opłacalności · zysk 0%</t>
   </si>
   <si>
-    <t>10 909 zł / MP · 2522 € / MP</t>
-  </si>
-  <si>
-    <t>rabat −19 323 zł (−3,85%)</t>
-  </si>
-  <si>
-    <t>maks. rabat −79 949 zł (−15,93%)</t>
+    <t>10 938 zł / MP · 2529 € / MP</t>
+  </si>
+  <si>
+    <t>rabat −19 415 zł (−3,86%)</t>
+  </si>
+  <si>
+    <t>maks. rabat −80 306 zł (−15,96%)</t>
   </si>
   <si>
     <t>Pole do negocjacji: o ile można zejść z ceny (2000 kg)</t>
@@ -138,7 +138,7 @@
     <t>KOB / GDW</t>
   </si>
   <si>
-    <t>0,5% / 2,5%</t>
+    <t>0,52% / 2,69%</t>
   </si>
   <si>
     <t>Opis wariantu</t>
@@ -399,13 +399,13 @@
     <t>KOB</t>
   </si>
   <si>
-    <t>0,5% ceny przed podatkiem (486 203 zł)</t>
+    <t>0,52% ceny przed podatkiem (487 377 zł)</t>
   </si>
   <si>
     <t>GDW</t>
   </si>
   <si>
-    <t>2,5% ceny przed podatkiem</t>
+    <t>2,69% ceny przed podatkiem</t>
   </si>
   <si>
     <t>Zysk 14%</t>
@@ -417,7 +417,7 @@
     <t>Zysk z narzutem (zysk + GDW)</t>
   </si>
   <si>
-    <t>zysk 14% + GDW 2,5%</t>
+    <t>zysk 14% + GDW 2,69%</t>
   </si>
   <si>
     <t>Podatek</t>
@@ -1358,15 +1358,15 @@
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
-        <v>501809.5481100001</v>
+        <v>503137.3101379699</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7">
-        <v>482486.38289686054</v>
+        <v>483722.677335943</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="8">
-        <v>421860.7820735052</v>
+        <v>422831.3290023131</v>
       </c>
       <c r="F6" s="8"/>
     </row>
@@ -1419,7 +1419,7 @@
         <v>0.14</v>
       </c>
       <c r="B11" s="14">
-        <v>501809.5481100001</v>
+        <v>503137.3101379699</v>
       </c>
       <c r="C11" s="14">
         <v>0</v>
@@ -1428,10 +1428,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="14">
-        <v>80223.44550000002</v>
+        <v>81318.86957832126</v>
       </c>
       <c r="F11" s="14">
-        <v>10908.90321978261</v>
+        <v>10937.767611694999</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1439,19 +1439,19 @@
         <v>0.12</v>
       </c>
       <c r="B12" s="17">
-        <v>488775.8837309412</v>
+        <v>490041.590842263</v>
       </c>
       <c r="C12" s="17">
-        <v>-13033.664379058871</v>
+        <v>-13095.719295706891</v>
       </c>
       <c r="D12" s="18">
-        <v>-0.025973328782101616</v>
+        <v>-0.026028122009309533</v>
       </c>
       <c r="E12" s="17">
-        <v>68840.5822882353</v>
+        <v>69883.32451751179</v>
       </c>
       <c r="F12" s="17">
-        <v>10625.56268980307</v>
+        <v>10653.078061788327</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1459,19 +1459,19 @@
         <v>0.11</v>
       </c>
       <c r="B13" s="20">
-        <v>482486.38289686054</v>
+        <v>483722.677335943</v>
       </c>
       <c r="C13" s="20">
-        <v>-19323.165213139553</v>
+        <v>-19414.63280202693</v>
       </c>
       <c r="D13" s="21">
-        <v>-0.03850696999672031</v>
+        <v>-0.038587145915899304</v>
       </c>
       <c r="E13" s="20">
-        <v>63347.68899418606</v>
+        <v>64365.474103554785</v>
       </c>
       <c r="F13" s="20">
-        <v>10488.834410801315</v>
+        <v>10515.710376868326</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1479,19 +1479,19 @@
         <v>0.1</v>
       </c>
       <c r="B14" s="23">
-        <v>476341.4682888506</v>
+        <v>477549.3609150219</v>
       </c>
       <c r="C14" s="23">
-        <v>-25468.07982114947</v>
+        <v>-25587.949222947995</v>
       </c>
       <c r="D14" s="24">
-        <v>-0.05075248152824444</v>
+        <v>-0.05085679139146188</v>
       </c>
       <c r="E14" s="23">
-        <v>57981.06910919541</v>
+        <v>58974.763100057615</v>
       </c>
       <c r="F14" s="23">
-        <v>10355.249310627187</v>
+        <v>10381.507845978736</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1499,19 +1499,19 @@
         <v>0.08</v>
       </c>
       <c r="B15" s="23">
-        <v>464465.9029789888</v>
+        <v>465619.84404756647</v>
       </c>
       <c r="C15" s="23">
-        <v>-37343.64513101132</v>
+        <v>-37517.46609040344</v>
       </c>
       <c r="D15" s="24">
-        <v>-0.07441796448804384</v>
+        <v>-0.0745670522428866</v>
       </c>
       <c r="E15" s="23">
-        <v>47609.623938202254</v>
+        <v>48557.57832302928</v>
       </c>
       <c r="F15" s="23">
-        <v>10097.08484736932</v>
+        <v>10122.170522773184</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1519,19 +1519,19 @@
         <v>0.06</v>
       </c>
       <c r="B16" s="23">
-        <v>453112.3405398901</v>
+        <v>454215.856557532</v>
       </c>
       <c r="C16" s="23">
-        <v>-48697.20757010998</v>
+        <v>-48921.45358043793</v>
       </c>
       <c r="D16" s="24">
-        <v>-0.09704320643862126</v>
+        <v>-0.09723280821098862</v>
       </c>
       <c r="E16" s="23">
-        <v>37694.066467032964</v>
+        <v>38599.30036437225</v>
       </c>
       <c r="F16" s="23">
-        <v>9850.268272606307</v>
+        <v>9874.257751250696</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1539,19 +1539,19 @@
         <v>0.04</v>
       </c>
       <c r="B17" s="23">
-        <v>442247.1033669893</v>
+        <v>443303.4202524128</v>
       </c>
       <c r="C17" s="23">
-        <v>-59562.4447430108</v>
+        <v>-59833.88988555712</v>
       </c>
       <c r="D17" s="24">
-        <v>-0.11869531970315221</v>
+        <v>-0.1189215919390862</v>
       </c>
       <c r="E17" s="23">
-        <v>28204.98458602151</v>
+        <v>29070.258524622845</v>
       </c>
       <c r="F17" s="23">
-        <v>9614.067464499767</v>
+        <v>9637.030875052453</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1559,19 +1559,19 @@
         <v>0.02</v>
       </c>
       <c r="B18" s="23">
-        <v>431839.3498645264</v>
+        <v>432851.4242977205</v>
       </c>
       <c r="C18" s="23">
-        <v>-69970.19824547367</v>
+        <v>-70285.88584024942</v>
       </c>
       <c r="D18" s="24">
-        <v>-0.1394357650407555</v>
+        <v>-0.1396952371132558</v>
       </c>
       <c r="E18" s="23">
-        <v>19115.442994736844</v>
+        <v>19943.285960812238</v>
       </c>
       <c r="F18" s="23">
-        <v>9387.811953576662</v>
+        <v>9409.813571689576</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1579,19 +1579,19 @@
         <v>0</v>
       </c>
       <c r="B19" s="26">
-        <v>421860.7820735052</v>
+        <v>422831.3290023131</v>
       </c>
       <c r="C19" s="26">
-        <v>-79948.76603649487</v>
+        <v>-80305.98113565682</v>
       </c>
       <c r="D19" s="27">
-        <v>-0.15932093428196298</v>
+        <v>-0.15961046719758346</v>
       </c>
       <c r="E19" s="26">
-        <v>10400.727860824743</v>
+        <v>11193.461023605374</v>
       </c>
       <c r="F19" s="26">
-        <v>9170.88656681533</v>
+        <v>9191.985413093762</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1804,10 +1804,10 @@
       <c r="C39" s="38"/>
       <c r="D39" s="38"/>
       <c r="E39" s="39">
-        <v>113200.25086602406</v>
+        <v>113498.94718522218</v>
       </c>
       <c r="F39" s="39">
-        <v>108853.26834744174</v>
+        <v>109131.3879130116</v>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2351,7 +2351,7 @@
       <c r="C32" s="53"/>
       <c r="D32" s="53"/>
       <c r="E32" s="57">
-        <v>2431.0135000000005</v>
+        <v>2509.992078683575</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2364,7 +2364,7 @@
       <c r="C33" s="50"/>
       <c r="D33" s="50"/>
       <c r="E33" s="56">
-        <v>12155.067500000003</v>
+        <v>13086.075206340582</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2377,7 +2377,7 @@
       <c r="C34" s="53"/>
       <c r="D34" s="53"/>
       <c r="E34" s="57">
-        <v>68068.37800000001</v>
+        <v>68232.7943719807</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -2390,7 +2390,7 @@
       <c r="C35" s="50"/>
       <c r="D35" s="50"/>
       <c r="E35" s="56">
-        <v>80223.44550000002</v>
+        <v>81318.86957832126</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2403,7 +2403,7 @@
       <c r="C36" s="53"/>
       <c r="D36" s="53"/>
       <c r="E36" s="57">
-        <v>15606.848110000003</v>
+        <v>15760.207480964978</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2416,7 +2416,7 @@
       <c r="C37" s="59"/>
       <c r="D37" s="59"/>
       <c r="E37" s="60">
-        <v>501809.5481100001</v>
+        <v>503137.3101379699</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2429,7 +2429,7 @@
       <c r="C38" s="59"/>
       <c r="D38" s="59"/>
       <c r="E38" s="60">
-        <v>421586.10261000006</v>
+        <v>421818.4405596487</v>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="153">
   <si>
     <t>KALKULACJA NK41</t>
   </si>
@@ -42,25 +42,37 @@
     <t>21.10.2026</t>
   </si>
   <si>
-    <t>Wygenerowano 27.10.2026, 14:28:47 · ceny netto w zł · szablon NK41</t>
-  </si>
-  <si>
-    <t>Cena ofertowa · zysk 14%</t>
+    <t>Wygenerowano 27.10.2026, 14:33:08 · ceny netto w zł · szablon NK41</t>
+  </si>
+  <si>
+    <t>Cena</t>
+  </si>
+  <si>
+    <t>Cena netto</t>
+  </si>
+  <si>
+    <t>Cena za MP</t>
+  </si>
+  <si>
+    <t>Rabat od oferty</t>
+  </si>
+  <si>
+    <t>Cena ofertowa · zysk 14% · 2000 kg · 2529 € / MP</t>
+  </si>
+  <si>
+    <t>–</t>
   </si>
   <si>
     <t>Można zejść do · zysk 11%</t>
   </si>
   <si>
-    <t>Próg opłacalności · zysk 0%</t>
-  </si>
-  <si>
-    <t>10 938 zł / MP · 2529 € / MP</t>
-  </si>
-  <si>
-    <t>rabat −19 415 zł (−3,86%)</t>
-  </si>
-  <si>
-    <t>maks. rabat −80 306 zł (−15,96%)</t>
+    <t>−19 415 zł (−3,86%)</t>
+  </si>
+  <si>
+    <t>Próg opłacalności · zysk 0% (maks. rabat)</t>
+  </si>
+  <si>
+    <t>−80 306 zł (−15,96%)</t>
   </si>
   <si>
     <t>Pole do negocjacji: o ile można zejść z ceny (2000 kg)</t>
@@ -69,21 +81,12 @@
     <t>Zysk</t>
   </si>
   <si>
-    <t>Cena netto</t>
-  </si>
-  <si>
-    <t>Rabat od oferty</t>
-  </si>
-  <si>
     <t>Rabat %</t>
   </si>
   <si>
     <t>Zysk z narzutem</t>
   </si>
   <si>
-    <t>Cena za MP</t>
-  </si>
-  <si>
     <t>Zielone: rabat bez zejścia poniżej zysku 11%. Żółte: poniżej zysku do porównania. Przy zysku 0% w cenie zostają koszty, KOB, GDW i podatek.</t>
   </si>
   <si>
@@ -138,7 +141,7 @@
     <t>KOB / GDW</t>
   </si>
   <si>
-    <t>0,52% / 2,69%</t>
+    <t>0,515% / 2,685%</t>
   </si>
   <si>
     <t>Opis wariantu</t>
@@ -183,37 +186,40 @@
     <t>nie wpisano ceny dla zwiększonego udźwigu</t>
   </si>
   <si>
-    <t>–</t>
-  </si>
-  <si>
     <t>Słupki e-ładowarek 3,7 kW</t>
   </si>
   <si>
     <t>46 MP × 1700 zł + montaż</t>
   </si>
   <si>
-    <t>Konserwacja · wariant 1 · 23 szt.</t>
-  </si>
-  <si>
-    <t>Konserwacja · wariant 2 · 23 szt.</t>
-  </si>
-  <si>
-    <t>40 zł / szt. / mies.</t>
-  </si>
-  <si>
-    <t>50 zł / szt. / mies.</t>
-  </si>
-  <si>
-    <t>11 040 zł rocznie</t>
-  </si>
-  <si>
-    <t>13 800 zł rocznie</t>
-  </si>
-  <si>
-    <t>jeden przegląd (co pół roku): 5520 zł</t>
-  </si>
-  <si>
-    <t>jeden przegląd (co pół roku): 6900 zł</t>
+    <t>Konserwacja (23 szt.)</t>
+  </si>
+  <si>
+    <t>Miesięcznie</t>
+  </si>
+  <si>
+    <t>Rocznie</t>
+  </si>
+  <si>
+    <t>Jeden przegląd (co pół roku)</t>
+  </si>
+  <si>
+    <t>35 zł / szt. / mies.</t>
+  </si>
+  <si>
+    <t>40 zł / szt. / mies.  · wariant 1</t>
+  </si>
+  <si>
+    <t>45 zł / szt. / mies.</t>
+  </si>
+  <si>
+    <t>50 zł / szt. / mies.  · wariant 2</t>
+  </si>
+  <si>
+    <t>55 zł / szt. / mies.</t>
+  </si>
+  <si>
+    <t>60 zł / szt. / mies.</t>
   </si>
   <si>
     <t>Pozostałe dane wejściowe</t>
@@ -243,7 +249,7 @@
     <t>4.325 / 3.86</t>
   </si>
   <si>
-    <t>Koszty krok po kroku · 2000 kg, zysk 14%</t>
+    <t>Koszty · 2000 kg · 14%</t>
   </si>
   <si>
     <t>Strona 1: obliczenia · strona 2: cennik szablonu NK41</t>
@@ -399,13 +405,13 @@
     <t>KOB</t>
   </si>
   <si>
-    <t>0,52% ceny przed podatkiem (487 377 zł)</t>
+    <t>0,515% ceny przed podatkiem (487 377 zł)</t>
   </si>
   <si>
     <t>GDW</t>
   </si>
   <si>
-    <t>2,69% ceny przed podatkiem</t>
+    <t>2,685% ceny przed podatkiem</t>
   </si>
   <si>
     <t>Zysk 14%</t>
@@ -417,7 +423,7 @@
     <t>Zysk z narzutem (zysk + GDW)</t>
   </si>
   <si>
-    <t>zysk 14% + GDW 2,69%</t>
+    <t>zysk 14% + GDW 2,685%</t>
   </si>
   <si>
     <t>Podatek</t>
@@ -497,7 +503,7 @@
     <numFmt numFmtId="170" formatCode="&quot;+&quot;#,##0 &quot;zł&quot;"/>
     <numFmt numFmtId="171" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -506,19 +512,19 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FFC4E4E7"/>
+      <color rgb="FF6A7780"/>
       <sz val="8"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="15"/>
+      <color rgb="FF0E171C"/>
+      <sz val="16"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF0E171C"/>
       <sz val="13"/>
       <name val="Arial"/>
     </font>
@@ -530,13 +536,18 @@
     <font>
       <b/>
       <color rgb="FF0A6B74"/>
-      <sz val="16"/>
+      <sz val="9"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FF0E171C"/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0E171C"/>
-      <sz val="16"/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -548,17 +559,6 @@
     <font>
       <b/>
       <color rgb="FF0A6B74"/>
-      <sz val="9"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF0A6B74"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FF0E171C"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -591,22 +591,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF0E171C"/>
-      <sz val="9.5"/>
-      <name val="Consolas"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF0E171C"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FF0E171C"/>
-      <sz val="9.5"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color rgb="FF6A7780"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -623,22 +607,12 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF0A6B74"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3F8F8"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -676,49 +650,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD3D9DD"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD3D9DD"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF0A6B74"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD3D9DD"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD3D9DD"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD3D9DD"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD3D9DD"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFD3D9DD"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -748,8 +685,8 @@
     <border>
       <left/>
       <right/>
-      <top style="medium">
-        <color rgb="FF0A6B74"/>
+      <top style="thin">
+        <color rgb="FFD3D9DD"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -767,197 +704,189 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="11" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="12" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="bottom" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="10" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1299,13 +1228,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="3" width="17" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="6" width="17" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1342,601 +1273,680 @@
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
     </row>
-    <row r="5" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="6"/>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="6"/>
+      <c r="D5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="6"/>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="F5" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="9">
         <v>503137.3101379699</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7">
+      <c r="E6" s="9">
+        <v>10937.767611694999</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="9">
         <v>483722.677335943</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="8">
+      <c r="E7" s="9">
+        <v>10515.710376868326</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="9">
         <v>422831.3290023131</v>
       </c>
-      <c r="F6" s="8"/>
-    </row>
-    <row r="7" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="E8" s="9">
+        <v>9191.985413093762</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+    </row>
+    <row r="11" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="9"/>
-    </row>
-    <row r="9" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-    </row>
-    <row r="10" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="12" t="s">
+      <c r="D11" s="13" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="13">
+      <c r="E11" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="14">
         <v>0.14</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B12" s="15">
         <v>503137.3101379699</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C12" s="15">
         <v>0</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D12" s="16">
         <v>0</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E12" s="15">
         <v>81318.86957832126</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F12" s="15">
         <v>10937.767611694999</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="16">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
         <v>0.12</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B13" s="18">
         <v>490041.590842263</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C13" s="18">
         <v>-13095.719295706891</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D13" s="19">
         <v>-0.026028122009309533</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E13" s="18">
         <v>69883.32451751179</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F13" s="18">
         <v>10653.078061788327</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="19">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="20">
         <v>0.11</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B14" s="21">
         <v>483722.677335943</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C14" s="21">
         <v>-19414.63280202693</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D14" s="22">
         <v>-0.038587145915899304</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E14" s="21">
         <v>64365.474103554785</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F14" s="21">
         <v>10515.710376868326</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="22">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="23">
         <v>0.1</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B15" s="24">
         <v>477549.3609150219</v>
       </c>
-      <c r="C14" s="23">
+      <c r="C15" s="24">
         <v>-25587.949222947995</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D15" s="25">
         <v>-0.05085679139146188</v>
       </c>
-      <c r="E14" s="23">
+      <c r="E15" s="24">
         <v>58974.763100057615</v>
       </c>
-      <c r="F14" s="23">
+      <c r="F15" s="24">
         <v>10381.507845978736</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="22">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="23">
         <v>0.08</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B16" s="24">
         <v>465619.84404756647</v>
       </c>
-      <c r="C15" s="23">
+      <c r="C16" s="24">
         <v>-37517.46609040344</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D16" s="25">
         <v>-0.0745670522428866</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E16" s="24">
         <v>48557.57832302928</v>
       </c>
-      <c r="F15" s="23">
+      <c r="F16" s="24">
         <v>10122.170522773184</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="22">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="23">
         <v>0.06</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B17" s="24">
         <v>454215.856557532</v>
       </c>
-      <c r="C16" s="23">
+      <c r="C17" s="24">
         <v>-48921.45358043793</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D17" s="25">
         <v>-0.09723280821098862</v>
       </c>
-      <c r="E16" s="23">
+      <c r="E17" s="24">
         <v>38599.30036437225</v>
       </c>
-      <c r="F16" s="23">
+      <c r="F17" s="24">
         <v>9874.257751250696</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="22">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="23">
         <v>0.04</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B18" s="24">
         <v>443303.4202524128</v>
       </c>
-      <c r="C17" s="23">
+      <c r="C18" s="24">
         <v>-59833.88988555712</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D18" s="25">
         <v>-0.1189215919390862</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E18" s="24">
         <v>29070.258524622845</v>
       </c>
-      <c r="F17" s="23">
+      <c r="F18" s="24">
         <v>9637.030875052453</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="22">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="23">
         <v>0.02</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B19" s="24">
         <v>432851.4242977205</v>
       </c>
-      <c r="C18" s="23">
+      <c r="C19" s="24">
         <v>-70285.88584024942</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D19" s="25">
         <v>-0.1396952371132558</v>
       </c>
-      <c r="E18" s="23">
+      <c r="E19" s="24">
         <v>19943.285960812238</v>
       </c>
-      <c r="F18" s="23">
+      <c r="F19" s="24">
         <v>9409.813571689576</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="26">
         <v>0</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B20" s="27">
         <v>422831.3290023131</v>
       </c>
-      <c r="C19" s="26">
+      <c r="C20" s="27">
         <v>-80305.98113565682</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D20" s="28">
         <v>-0.15961046719758346</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E20" s="27">
         <v>11193.461023605374</v>
       </c>
-      <c r="F19" s="26">
+      <c r="F20" s="27">
         <v>9191.985413093762</v>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-    </row>
-    <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+    <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="29" t="s">
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29" t="s">
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="30" t="s">
         <v>21</v>
-      </c>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-    </row>
-    <row r="24" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="30" t="s">
-        <v>22</v>
       </c>
       <c r="B24" s="30"/>
       <c r="C24" s="30"/>
       <c r="D24" s="30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E24" s="30"/>
       <c r="F24" s="30"/>
     </row>
-    <row r="25" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+    </row>
+    <row r="26" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-    </row>
-    <row r="26" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="30" t="s">
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30" t="s">
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+    </row>
+    <row r="27" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-    </row>
-    <row r="27" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="32" t="s">
+      <c r="B27" s="31"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32" t="s">
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+    </row>
+    <row r="28" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-    </row>
-    <row r="28" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="B28" s="33"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30" t="s">
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+    </row>
+    <row r="29" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-    </row>
-    <row r="29" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="32" t="s">
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="32"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32" t="s">
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+    </row>
+    <row r="30" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="E29" s="32"/>
-      <c r="F29" s="32"/>
-    </row>
-    <row r="30" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="30" t="s">
+      <c r="B30" s="33"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30" t="s">
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
+    </row>
+    <row r="31" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-    </row>
-    <row r="31" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="32"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32" t="s">
+      <c r="B31" s="31"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="33" t="s">
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
+    </row>
+    <row r="32" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" s="33"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="34" t="s">
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="35" t="s">
+      <c r="B34" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="35"/>
-      <c r="C34" s="35" t="s">
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="36" t="s">
         <v>40</v>
-      </c>
-      <c r="D34" s="35"/>
-      <c r="E34" s="35" t="s">
-        <v>41</v>
-      </c>
-      <c r="F34" s="35"/>
-    </row>
-    <row r="35" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="36" t="s">
-        <v>42</v>
       </c>
       <c r="B35" s="36"/>
       <c r="C35" s="36" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D35" s="36"/>
       <c r="E35" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="F35" s="36"/>
+    </row>
+    <row r="36" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="37"/>
+      <c r="C36" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="F35" s="36"/>
-    </row>
-    <row r="37" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
+      <c r="D36" s="37"/>
+      <c r="E36" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="F36" s="37"/>
+    </row>
+    <row r="38" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="12" t="s">
+      <c r="B38" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="F37" s="12" t="s">
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="13" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="37" t="s">
+      <c r="F38" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B38" s="38" t="s">
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="C38" s="38"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="39" t="s">
+      <c r="B39" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="39" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="37" t="s">
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" s="40" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="38" t="s">
+      <c r="B40" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C39" s="38"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="39">
+      <c r="C40" s="39"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="40">
         <v>113498.94718522218</v>
       </c>
-      <c r="F39" s="39">
+      <c r="F40" s="40">
         <v>109131.3879130116</v>
       </c>
     </row>
-    <row r="41" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="40" t="s">
+    <row r="42" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="B41" s="40"/>
-      <c r="C41" s="40"/>
-      <c r="D41" s="40" t="s">
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="E41" s="40"/>
-      <c r="F41" s="40"/>
-    </row>
-    <row r="42" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="41" t="s">
+      <c r="E42" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B42" s="41"/>
-      <c r="C42" s="41"/>
-      <c r="D42" s="41" t="s">
+      <c r="F42" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="E42" s="41"/>
-      <c r="F42" s="41"/>
-    </row>
-    <row r="43" ht="17" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="42" t="s">
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B43" s="42"/>
-      <c r="C43" s="42"/>
-      <c r="D43" s="42" t="s">
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="41">
+        <v>805</v>
+      </c>
+      <c r="E43" s="41">
+        <v>9660</v>
+      </c>
+      <c r="F43" s="41">
+        <v>4830</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="E43" s="42"/>
-      <c r="F43" s="42"/>
-    </row>
-    <row r="44" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="43" t="s">
+      <c r="B44" s="42"/>
+      <c r="C44" s="42"/>
+      <c r="D44" s="9">
+        <v>920</v>
+      </c>
+      <c r="E44" s="9">
+        <v>11040</v>
+      </c>
+      <c r="F44" s="9">
+        <v>5520</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B44" s="43"/>
-      <c r="C44" s="43"/>
-      <c r="D44" s="43" t="s">
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="41">
+        <v>1035</v>
+      </c>
+      <c r="E45" s="41">
+        <v>12420</v>
+      </c>
+      <c r="F45" s="41">
+        <v>6210</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="E44" s="43"/>
-      <c r="F44" s="43"/>
-    </row>
-    <row r="46" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="10" t="s">
+      <c r="B46" s="42"/>
+      <c r="C46" s="42"/>
+      <c r="D46" s="9">
+        <v>1150</v>
+      </c>
+      <c r="E46" s="9">
+        <v>13800</v>
+      </c>
+      <c r="F46" s="9">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="44" t="s">
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="41">
+        <v>1265</v>
+      </c>
+      <c r="E47" s="41">
+        <v>15180</v>
+      </c>
+      <c r="F47" s="41">
+        <v>7590</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B47" s="45" t="s">
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="41">
+        <v>1380</v>
+      </c>
+      <c r="E48" s="41">
+        <v>16560</v>
+      </c>
+      <c r="F48" s="41">
+        <v>8280</v>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="C47" s="45"/>
-      <c r="D47" s="45"/>
-      <c r="E47" s="45"/>
-      <c r="F47" s="45"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="44" t="s">
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="B48" s="45" t="s">
+      <c r="B51" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="C48" s="45"/>
-      <c r="D48" s="45"/>
-      <c r="E48" s="45"/>
-      <c r="F48" s="45"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="44" t="s">
+      <c r="C51" s="44"/>
+      <c r="D51" s="44"/>
+      <c r="E51" s="44"/>
+      <c r="F51" s="44"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="B49" s="45" t="s">
+      <c r="B52" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="C49" s="45"/>
-      <c r="D49" s="45"/>
-      <c r="E49" s="45"/>
-      <c r="F49" s="45"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="44" t="s">
+      <c r="C52" s="44"/>
+      <c r="D52" s="44"/>
+      <c r="E52" s="44"/>
+      <c r="F52" s="44"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B50" s="45" t="s">
+      <c r="B53" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="C50" s="45"/>
-      <c r="D50" s="45"/>
-      <c r="E50" s="45"/>
-      <c r="F50" s="45"/>
+      <c r="C53" s="44"/>
+      <c r="D53" s="44"/>
+      <c r="E53" s="44"/>
+      <c r="F53" s="44"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="B54" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="C54" s="44"/>
+      <c r="D54" s="44"/>
+      <c r="E54" s="44"/>
+      <c r="F54" s="44"/>
     </row>
   </sheetData>
-  <mergeCells count="58">
+  <mergeCells count="52">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="A25:C25"/>
@@ -1953,29 +1963,30 @@
     <mergeCell ref="D30:F30"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="D31:F31"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="B34:F34"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="E35:F35"/>
-    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E36:F36"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B39:D39"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="B40:D40"/>
     <mergeCell ref="A42:C42"/>
-    <mergeCell ref="D42:F42"/>
     <mergeCell ref="A43:C43"/>
-    <mergeCell ref="D43:F43"/>
     <mergeCell ref="A44:C44"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B54:F54"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.25" footer="0.25"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="80" fitToWidth="1" fitToHeight="1"/>
@@ -1994,550 +2005,550 @@
     <col min="2" max="5" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
+    <row r="1" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
+      <c r="A2" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
+      <c r="A4" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" s="45" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
+      <c r="A5" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="43" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="43" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="49">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="50" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="52">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="49">
+        <v>19.6338</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="52">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="47" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="53">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="52">
         <v>76</v>
       </c>
-      <c r="B6" s="45" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="44" t="s">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="48" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" s="48"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="54">
+        <v>348801</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" s="51" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="55">
+        <v>4113.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="48"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="54">
+        <v>9880</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="55">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="C25" s="48"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="54">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="50" t="s">
+        <v>113</v>
+      </c>
+      <c r="B26" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C26" s="51"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="55">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="54">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="B28" s="51" t="s">
+        <v>118</v>
+      </c>
+      <c r="C28" s="51"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="55">
+        <v>7053.52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="C29" s="48"/>
+      <c r="D29" s="48"/>
+      <c r="E29" s="54">
+        <v>20240</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="50" t="s">
+        <v>120</v>
+      </c>
+      <c r="B30" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="C30" s="51"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="55">
+        <v>3160.521</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="56" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" s="57"/>
+      <c r="D31" s="57"/>
+      <c r="E31" s="58">
+        <v>403548.24100000004</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="50" t="s">
+        <v>124</v>
+      </c>
+      <c r="B32" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="C32" s="51"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="55">
+        <v>2509.992078683575</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="47" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="54">
+        <v>13086.075206340582</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="B34" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="C34" s="51"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="55">
+        <v>68232.7943719807</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="47" t="s">
+        <v>130</v>
+      </c>
+      <c r="B35" s="48" t="s">
+        <v>131</v>
+      </c>
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="54">
+        <v>81318.86957832126</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="50" t="s">
+        <v>132</v>
+      </c>
+      <c r="B36" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="55">
+        <v>15760.207480964978</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="56" t="s">
+        <v>134</v>
+      </c>
+      <c r="B37" s="57" t="s">
+        <v>135</v>
+      </c>
+      <c r="C37" s="57"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="58">
+        <v>503137.3101379699</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="56" t="s">
+        <v>136</v>
+      </c>
+      <c r="B38" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="C38" s="57"/>
+      <c r="D38" s="57"/>
+      <c r="E38" s="58">
+        <v>421818.4405596487</v>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="45" t="s">
+        <v>138</v>
+      </c>
+      <c r="B39" s="45"/>
+      <c r="C39" s="45"/>
+      <c r="D39" s="45"/>
+      <c r="E39" s="45"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="B40" s="46"/>
+      <c r="C40" s="46"/>
+      <c r="D40" s="46"/>
+      <c r="E40" s="46"/>
+    </row>
+    <row r="42" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="59" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="60" t="s">
+        <v>35</v>
+      </c>
+      <c r="C42" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="B7" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="44" t="s">
+      <c r="D42" s="61"/>
+      <c r="E42" s="62" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="43" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="61" t="s">
+        <v>141</v>
+      </c>
+      <c r="B43" s="63">
+        <v>130</v>
+      </c>
+      <c r="C43" s="61" t="s">
         <v>80</v>
       </c>
-      <c r="B8" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="44" t="s">
+      <c r="D43" s="61"/>
+      <c r="E43" s="62" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="44" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="61" t="s">
+        <v>143</v>
+      </c>
+      <c r="B44" s="63">
+        <v>45</v>
+      </c>
+      <c r="C44" s="61" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="44" t="s">
+      <c r="D44" s="61"/>
+      <c r="E44" s="62" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="45" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="59" t="s">
+        <v>145</v>
+      </c>
+      <c r="B45" s="60" t="s">
+        <v>35</v>
+      </c>
+      <c r="C45" s="61" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="44" t="s">
-        <v>86</v>
-      </c>
-      <c r="B11" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-    </row>
-    <row r="13" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-    </row>
-    <row r="14" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="B14" s="47" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="48" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="49" t="s">
-        <v>91</v>
-      </c>
-      <c r="B15" s="50" t="s">
-        <v>92</v>
-      </c>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="51">
-        <v>50.6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="52" t="s">
-        <v>93</v>
-      </c>
-      <c r="B16" s="53" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" s="53"/>
-      <c r="D16" s="53"/>
-      <c r="E16" s="54">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="49" t="s">
-        <v>95</v>
-      </c>
-      <c r="B17" s="50" t="s">
-        <v>96</v>
-      </c>
-      <c r="C17" s="50"/>
-      <c r="D17" s="50"/>
-      <c r="E17" s="51">
-        <v>19.6338</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="52" t="s">
-        <v>97</v>
-      </c>
-      <c r="B18" s="53" t="s">
-        <v>98</v>
-      </c>
-      <c r="C18" s="53"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="54">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="B19" s="50" t="s">
-        <v>100</v>
-      </c>
-      <c r="C19" s="50"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="55">
-        <v>3640</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="52" t="s">
-        <v>101</v>
-      </c>
-      <c r="B20" s="53" t="s">
-        <v>102</v>
-      </c>
-      <c r="C20" s="53"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="54">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="50" t="s">
-        <v>103</v>
-      </c>
-      <c r="C21" s="50"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="56">
-        <v>348801</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="52" t="s">
-        <v>104</v>
-      </c>
-      <c r="B22" s="53" t="s">
-        <v>105</v>
-      </c>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="57">
-        <v>4113.2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="B23" s="50" t="s">
-        <v>107</v>
-      </c>
-      <c r="C23" s="50"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="56">
-        <v>9880</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="52" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="53" t="s">
-        <v>108</v>
-      </c>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="57">
-        <v>3200</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="49" t="s">
-        <v>109</v>
-      </c>
-      <c r="B25" s="50" t="s">
-        <v>110</v>
-      </c>
-      <c r="C25" s="50"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="56">
-        <v>4800</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="52" t="s">
-        <v>111</v>
-      </c>
-      <c r="B26" s="53" t="s">
-        <v>112</v>
-      </c>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="57">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="49" t="s">
-        <v>113</v>
-      </c>
-      <c r="B27" s="50" t="s">
-        <v>114</v>
-      </c>
-      <c r="C27" s="50"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="56">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="52" t="s">
-        <v>115</v>
-      </c>
-      <c r="B28" s="53" t="s">
-        <v>116</v>
-      </c>
-      <c r="C28" s="53"/>
-      <c r="D28" s="53"/>
-      <c r="E28" s="57">
-        <v>7053.52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="49" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="50" t="s">
-        <v>117</v>
-      </c>
-      <c r="C29" s="50"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="56">
-        <v>20240</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="52" t="s">
-        <v>118</v>
-      </c>
-      <c r="B30" s="53" t="s">
-        <v>119</v>
-      </c>
-      <c r="C30" s="53"/>
-      <c r="D30" s="53"/>
-      <c r="E30" s="57">
-        <v>3160.521</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="58" t="s">
-        <v>120</v>
-      </c>
-      <c r="B31" s="59" t="s">
-        <v>121</v>
-      </c>
-      <c r="C31" s="59"/>
-      <c r="D31" s="59"/>
-      <c r="E31" s="60">
-        <v>403548.24100000004</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="52" t="s">
-        <v>122</v>
-      </c>
-      <c r="B32" s="53" t="s">
-        <v>123</v>
-      </c>
-      <c r="C32" s="53"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="57">
-        <v>2509.992078683575</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="49" t="s">
-        <v>124</v>
-      </c>
-      <c r="B33" s="50" t="s">
-        <v>125</v>
-      </c>
-      <c r="C33" s="50"/>
-      <c r="D33" s="50"/>
-      <c r="E33" s="56">
-        <v>13086.075206340582</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="B34" s="53" t="s">
-        <v>127</v>
-      </c>
-      <c r="C34" s="53"/>
-      <c r="D34" s="53"/>
-      <c r="E34" s="57">
-        <v>68232.7943719807</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="49" t="s">
-        <v>128</v>
-      </c>
-      <c r="B35" s="50" t="s">
-        <v>129</v>
-      </c>
-      <c r="C35" s="50"/>
-      <c r="D35" s="50"/>
-      <c r="E35" s="56">
-        <v>81318.86957832126</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="52" t="s">
-        <v>130</v>
-      </c>
-      <c r="B36" s="53" t="s">
-        <v>131</v>
-      </c>
-      <c r="C36" s="53"/>
-      <c r="D36" s="53"/>
-      <c r="E36" s="57">
-        <v>15760.207480964978</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="58" t="s">
-        <v>132</v>
-      </c>
-      <c r="B37" s="59" t="s">
-        <v>133</v>
-      </c>
-      <c r="C37" s="59"/>
-      <c r="D37" s="59"/>
-      <c r="E37" s="60">
-        <v>503137.3101379699</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="58" t="s">
-        <v>134</v>
-      </c>
-      <c r="B38" s="59" t="s">
-        <v>135</v>
-      </c>
-      <c r="C38" s="59"/>
-      <c r="D38" s="59"/>
-      <c r="E38" s="60">
-        <v>421818.4405596487</v>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="46" t="s">
-        <v>136</v>
-      </c>
-      <c r="B39" s="46"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="46"/>
-      <c r="E39" s="46"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-    </row>
-    <row r="42" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="62" t="s">
-        <v>34</v>
-      </c>
-      <c r="C42" s="63" t="s">
-        <v>76</v>
-      </c>
-      <c r="D42" s="63"/>
-      <c r="E42" s="64" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="43" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="63" t="s">
-        <v>139</v>
-      </c>
-      <c r="B43" s="65">
-        <v>130</v>
-      </c>
-      <c r="C43" s="63" t="s">
-        <v>78</v>
-      </c>
-      <c r="D43" s="63"/>
-      <c r="E43" s="64" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="44" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="63" t="s">
-        <v>141</v>
-      </c>
-      <c r="B44" s="65">
-        <v>45</v>
-      </c>
-      <c r="C44" s="63" t="s">
-        <v>80</v>
-      </c>
-      <c r="D44" s="63"/>
-      <c r="E44" s="64" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="45" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="61" t="s">
-        <v>143</v>
-      </c>
-      <c r="B45" s="62" t="s">
-        <v>34</v>
-      </c>
-      <c r="C45" s="63" t="s">
-        <v>82</v>
-      </c>
-      <c r="D45" s="63"/>
-      <c r="E45" s="64" t="s">
-        <v>144</v>
+      <c r="D45" s="61"/>
+      <c r="E45" s="62" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="46" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="63" t="s">
-        <v>145</v>
-      </c>
-      <c r="B46" s="64" t="s">
-        <v>146</v>
-      </c>
-      <c r="C46" s="61" t="s">
+      <c r="A46" s="61" t="s">
         <v>147</v>
       </c>
-      <c r="D46" s="61"/>
-      <c r="E46" s="62" t="s">
-        <v>34</v>
+      <c r="B46" s="62" t="s">
+        <v>148</v>
+      </c>
+      <c r="C46" s="59" t="s">
+        <v>149</v>
+      </c>
+      <c r="D46" s="59"/>
+      <c r="E46" s="60" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="47" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="61" t="s">
-        <v>148</v>
-      </c>
-      <c r="B47" s="62" t="s">
-        <v>34</v>
-      </c>
-      <c r="C47" s="63" t="s">
-        <v>149</v>
-      </c>
-      <c r="D47" s="63"/>
-      <c r="E47" s="64" t="s">
+      <c r="A47" s="59" t="s">
         <v>150</v>
+      </c>
+      <c r="B47" s="60" t="s">
+        <v>35</v>
+      </c>
+      <c r="C47" s="61" t="s">
+        <v>151</v>
+      </c>
+      <c r="D47" s="61"/>
+      <c r="E47" s="62" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
@@ -39,10 +39,10 @@
     <t>ul. Leśna 5, Wrocław</t>
   </si>
   <si>
-    <t>21.10.2026</t>
-  </si>
-  <si>
-    <t>Wygenerowano 27.10.2026, 14:33:08 · ceny netto w zł · szablon NK41</t>
+    <t>21.10.2026, 14:43</t>
+  </si>
+  <si>
+    <t>Wygenerowano 27.10.2026, 14:43:39 · ceny netto w zł · szablon NK41</t>
   </si>
   <si>
     <t>Cena</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
@@ -39,10 +39,10 @@
     <t>ul. Leśna 5, Wrocław</t>
   </si>
   <si>
-    <t>21.10.2026, 14:43</t>
-  </si>
-  <si>
-    <t>Wygenerowano 27.10.2026, 14:43:39 · ceny netto w zł · szablon NK41</t>
+    <t>21.10.2026, 17:30</t>
+  </si>
+  <si>
+    <t>Wygenerowano 27.10.2026, 17:30:55 · ceny netto w zł · szablon NK41</t>
   </si>
   <si>
     <t>Cena</t>
@@ -294,7 +294,7 @@
     <t>348 801 zł</t>
   </si>
   <si>
-    <t>Suma 2500 kg (+0%)</t>
+    <t>Suma 2500 kg (nie wpisano dopłaty)</t>
   </si>
   <si>
     <t>Montaż, narzuty i cena</t>
@@ -650,7 +650,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -700,6 +700,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FFD3D9DD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -880,13 +889,13 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
@@ -39,10 +39,10 @@
     <t>ul. Leśna 5, Wrocław</t>
   </si>
   <si>
-    <t>21.10.2026, 17:30</t>
-  </si>
-  <si>
-    <t>Wygenerowano 27.10.2026, 17:30:55 · ceny netto w zł · szablon NK41</t>
+    <t>21.10.2026, 10:10</t>
+  </si>
+  <si>
+    <t>Wygenerowano 30.10.2026, 10:10:16 · ceny netto w zł · szablon NK41</t>
   </si>
   <si>
     <t>Cena</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
@@ -4,29 +4,12 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Podsumowanie" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Obliczenia i cennik" state="visible" r:id="rId5"/>
+    <sheet sheetId="1" name="Kalkulacja" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="B43" authorId="0">
-      <text/>
-    </comment>
-    <comment ref="B44" authorId="0">
-      <text/>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="153">
   <si>
@@ -39,10 +22,10 @@
     <t>ul. Leśna 5, Wrocław</t>
   </si>
   <si>
-    <t>21.10.2026, 10:10</t>
-  </si>
-  <si>
-    <t>Wygenerowano 30.10.2026, 10:10:16 · ceny netto w zł · szablon NK41</t>
+    <t>21.10.2026, 10:28</t>
+  </si>
+  <si>
+    <t>Wygenerowano 30.10.2026, 10:28:00 · ceny netto w zł · szablon NK41</t>
   </si>
   <si>
     <t>Cena</t>
@@ -222,6 +205,201 @@
     <t>60 zł / szt. / mies.</t>
   </si>
   <si>
+    <t>Koszty · 2000 kg · 14%</t>
+  </si>
+  <si>
+    <t>Skąd się biorą kwoty (wariant 2000 kg) · ceny netto w zł</t>
+  </si>
+  <si>
+    <t>Materiały i urządzenia</t>
+  </si>
+  <si>
+    <t>Platformy NK41: 23 × 12000 zł</t>
+  </si>
+  <si>
+    <t>276 000 zł</t>
+  </si>
+  <si>
+    <t>Hydraulika (siłownik 850 + rury i złączki 470 + wąż 100)</t>
+  </si>
+  <si>
+    <t>32 660 zł</t>
+  </si>
+  <si>
+    <t>Agregat hydrauliczny</t>
+  </si>
+  <si>
+    <t>20 241 zł</t>
+  </si>
+  <si>
+    <t>Sterowanie i elektryka: na agregat</t>
+  </si>
+  <si>
+    <t>8400 zł</t>
+  </si>
+  <si>
+    <t>Sterowanie i elektryka: na urządzenie</t>
+  </si>
+  <si>
+    <t>11 500 zł</t>
+  </si>
+  <si>
+    <t>Suma 2000 kg</t>
+  </si>
+  <si>
+    <t>348 801 zł</t>
+  </si>
+  <si>
+    <t>Suma 2500 kg (nie wpisano dopłaty)</t>
+  </si>
+  <si>
+    <t>Montaż, narzuty i cena</t>
+  </si>
+  <si>
+    <t>Pozycja</t>
+  </si>
+  <si>
+    <t>Skąd ta kwota</t>
+  </si>
+  <si>
+    <t>Kwota</t>
+  </si>
+  <si>
+    <t>Osobodni montażu</t>
+  </si>
+  <si>
+    <t>z cennika osobodni na urządzenie + utrudnienia</t>
+  </si>
+  <si>
+    <t>Tygodnie / dni montażu</t>
+  </si>
+  <si>
+    <t>tygodniowe wyjazdy ekipy</t>
+  </si>
+  <si>
+    <t>Osobodni podróży i rozładunku</t>
+  </si>
+  <si>
+    <t>pomiary, odbiory, rozładunek i dojazdy ekipy</t>
+  </si>
+  <si>
+    <t>Dni pracy ekipy</t>
+  </si>
+  <si>
+    <t>(osd montażu + podróży) ÷ 4 os.</t>
+  </si>
+  <si>
+    <t>Kilometry auta</t>
+  </si>
+  <si>
+    <t>dojazdy na montaż, pomiary i odbiory w obie strony</t>
+  </si>
+  <si>
+    <t>Noclegi (osobonoce)</t>
+  </si>
+  <si>
+    <t>(dni pracy + 1) × 4 os.</t>
+  </si>
+  <si>
+    <t>cena urządzeń i pozycji kosztowych (patrz wyżej)</t>
+  </si>
+  <si>
+    <t>Paliwo</t>
+  </si>
+  <si>
+    <t>3640 km × 113 zł/100 km (12 l × 9,4 zł)</t>
+  </si>
+  <si>
+    <t>Hotel</t>
+  </si>
+  <si>
+    <t>76 noclegów × 130 zł/doba</t>
+  </si>
+  <si>
+    <t>1 TIR × 3200 zł</t>
+  </si>
+  <si>
+    <t>Spider Crane</t>
+  </si>
+  <si>
+    <t>2 dni × 2400 zł/dzień</t>
+  </si>
+  <si>
+    <t>Rozładunek, sprzęt</t>
+  </si>
+  <si>
+    <t>1500 zł × 1 transp.</t>
+  </si>
+  <si>
+    <t>Rozładunek, ludzie</t>
+  </si>
+  <si>
+    <t>0,5 dni × 4 os. × 400 zł</t>
+  </si>
+  <si>
+    <t>Dojazdy, ludzie</t>
+  </si>
+  <si>
+    <t>17,63 osd podróży × 400 zł</t>
+  </si>
+  <si>
+    <t>50,6 osd × 400 zł (średnia stawka)</t>
+  </si>
+  <si>
+    <t>Diety</t>
+  </si>
+  <si>
+    <t>70,23 osd × 45 zł</t>
+  </si>
+  <si>
+    <t>Suma przed narzutami</t>
+  </si>
+  <si>
+    <t>suma kosztów powyżej</t>
+  </si>
+  <si>
+    <t>KOB</t>
+  </si>
+  <si>
+    <t>0,515% ceny przed podatkiem (487 377 zł)</t>
+  </si>
+  <si>
+    <t>GDW</t>
+  </si>
+  <si>
+    <t>2,685% ceny przed podatkiem</t>
+  </si>
+  <si>
+    <t>Zysk 14%</t>
+  </si>
+  <si>
+    <t>14% ceny przed podatkiem</t>
+  </si>
+  <si>
+    <t>Zysk z narzutem (zysk + GDW)</t>
+  </si>
+  <si>
+    <t>zysk 14% + GDW 2,685%</t>
+  </si>
+  <si>
+    <t>Podatek</t>
+  </si>
+  <si>
+    <t>14% od robocizny (31 254 zł) i zysku z narzutem</t>
+  </si>
+  <si>
+    <t>Cena kontraktu, zysk 14%</t>
+  </si>
+  <si>
+    <t>suma ÷ (1 − KOB − GDW − zysk) + podatek</t>
+  </si>
+  <si>
+    <t>Koszt rzeczywisty</t>
+  </si>
+  <si>
+    <t>cena − zysk z narzutem</t>
+  </si>
+  <si>
     <t>Pozostałe dane wejściowe</t>
   </si>
   <si>
@@ -249,205 +427,10 @@
     <t>4.325 / 3.86</t>
   </si>
   <si>
-    <t>Koszty · 2000 kg · 14%</t>
-  </si>
-  <si>
-    <t>Strona 1: obliczenia · strona 2: cennik szablonu NK41</t>
-  </si>
-  <si>
-    <t>Materiały i urządzenia</t>
-  </si>
-  <si>
-    <t>Platformy NK41: 23 × 12000 zł</t>
-  </si>
-  <si>
-    <t>276 000 zł</t>
-  </si>
-  <si>
-    <t>Hydraulika (siłownik 850 + rury i złączki 470 + wąż 100)</t>
-  </si>
-  <si>
-    <t>32 660 zł</t>
-  </si>
-  <si>
-    <t>Agregat hydrauliczny</t>
-  </si>
-  <si>
-    <t>20 241 zł</t>
-  </si>
-  <si>
-    <t>Sterowanie i elektryka: na agregat</t>
-  </si>
-  <si>
-    <t>8400 zł</t>
-  </si>
-  <si>
-    <t>Sterowanie i elektryka: na urządzenie</t>
-  </si>
-  <si>
-    <t>11 500 zł</t>
-  </si>
-  <si>
-    <t>Suma 2000 kg</t>
-  </si>
-  <si>
-    <t>348 801 zł</t>
-  </si>
-  <si>
-    <t>Suma 2500 kg (nie wpisano dopłaty)</t>
-  </si>
-  <si>
-    <t>Montaż, narzuty i cena</t>
-  </si>
-  <si>
-    <t>Pozycja</t>
-  </si>
-  <si>
-    <t>Skąd ta kwota</t>
-  </si>
-  <si>
-    <t>Kwota</t>
-  </si>
-  <si>
-    <t>Osobodni montażu</t>
-  </si>
-  <si>
-    <t>z cennika osobodni na urządzenie + utrudnienia</t>
-  </si>
-  <si>
-    <t>Tygodnie / dni montażu</t>
-  </si>
-  <si>
-    <t>tygodniowe wyjazdy ekipy</t>
-  </si>
-  <si>
-    <t>Osobodni podróży i rozładunku</t>
-  </si>
-  <si>
-    <t>pomiary, odbiory, rozładunek i dojazdy ekipy</t>
-  </si>
-  <si>
-    <t>Dni pracy ekipy</t>
-  </si>
-  <si>
-    <t>(osd montażu + podróży) ÷ 4 os.</t>
-  </si>
-  <si>
-    <t>Kilometry auta</t>
-  </si>
-  <si>
-    <t>dojazdy na montaż, pomiary i odbiory w obie strony</t>
-  </si>
-  <si>
-    <t>Noclegi (osobonoce)</t>
-  </si>
-  <si>
-    <t>(dni pracy + 1) × 4 os.</t>
-  </si>
-  <si>
-    <t>cena urządzeń i pozycji kosztowych (patrz wyżej)</t>
-  </si>
-  <si>
-    <t>Paliwo</t>
-  </si>
-  <si>
-    <t>3640 km × 113 zł/100 km (12 l × 9,4 zł)</t>
-  </si>
-  <si>
-    <t>Hotel</t>
-  </si>
-  <si>
-    <t>76 noclegów × 130 zł/doba</t>
-  </si>
-  <si>
-    <t>1 TIR × 3200 zł</t>
-  </si>
-  <si>
-    <t>Spider Crane</t>
-  </si>
-  <si>
-    <t>2 dni × 2400 zł/dzień</t>
-  </si>
-  <si>
-    <t>Rozładunek, sprzęt</t>
-  </si>
-  <si>
-    <t>1500 zł × 1 transp.</t>
-  </si>
-  <si>
-    <t>Rozładunek, ludzie</t>
-  </si>
-  <si>
-    <t>0,5 dni × 4 os. × 400 zł</t>
-  </si>
-  <si>
-    <t>Dojazdy, ludzie</t>
-  </si>
-  <si>
-    <t>17,63 osd podróży × 400 zł</t>
-  </si>
-  <si>
-    <t>50,6 osd × 400 zł (średnia stawka)</t>
-  </si>
-  <si>
-    <t>Diety</t>
-  </si>
-  <si>
-    <t>70,23 osd × 45 zł</t>
-  </si>
-  <si>
-    <t>Suma przed narzutami</t>
-  </si>
-  <si>
-    <t>suma kosztów powyżej</t>
-  </si>
-  <si>
-    <t>KOB</t>
-  </si>
-  <si>
-    <t>0,515% ceny przed podatkiem (487 377 zł)</t>
-  </si>
-  <si>
-    <t>GDW</t>
-  </si>
-  <si>
-    <t>2,685% ceny przed podatkiem</t>
-  </si>
-  <si>
-    <t>Zysk 14%</t>
-  </si>
-  <si>
-    <t>14% ceny przed podatkiem</t>
-  </si>
-  <si>
-    <t>Zysk z narzutem (zysk + GDW)</t>
-  </si>
-  <si>
-    <t>zysk 14% + GDW 2,685%</t>
-  </si>
-  <si>
-    <t>Podatek</t>
-  </si>
-  <si>
-    <t>14% od robocizny (31 254 zł) i zysku z narzutem</t>
-  </si>
-  <si>
-    <t>Cena kontraktu, zysk 14%</t>
-  </si>
-  <si>
-    <t>suma ÷ (1 − KOB − GDW − zysk) + podatek</t>
-  </si>
-  <si>
-    <t>Koszt rzeczywisty</t>
-  </si>
-  <si>
-    <t>cena − zysk z narzutem</t>
-  </si>
-  <si>
     <t>Cennik szablonu NK41</t>
   </si>
   <si>
-    <t>Pomarańczowe = zmienione względem domyślnego NK38</t>
+    <t>Pomarańczowe = zmienione względem domyślnego NK41</t>
   </si>
   <si>
     <t>1420 PLN</t>
@@ -713,7 +696,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
@@ -839,17 +822,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
@@ -890,13 +873,19 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment indent="1"/>
+      <alignment indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment indent="1"/>
+    </xf>
     <xf numFmtId="171" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment indent="3"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1237,7 +1226,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1884,66 +1873,656 @@
         <v>8280</v>
       </c>
     </row>
-    <row r="50" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="11" t="s">
+    <row r="50" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="B50" s="11"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
+      <c r="B50" s="43"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="43"/>
+      <c r="F50" s="43"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="43" t="s">
+      <c r="A51" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="B51" s="44" t="s">
-        <v>66</v>
-      </c>
+      <c r="B51" s="44"/>
       <c r="C51" s="44"/>
       <c r="D51" s="44"/>
       <c r="E51" s="44"/>
       <c r="F51" s="44"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="43" t="s">
+    <row r="53" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="B52" s="44" t="s">
+      <c r="B54" s="45"/>
+      <c r="C54" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="C52" s="44"/>
-      <c r="D52" s="44"/>
-      <c r="E52" s="44"/>
-      <c r="F52" s="44"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="43" t="s">
+      <c r="D54" s="46"/>
+      <c r="E54" s="46"/>
+      <c r="F54" s="46"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="B53" s="44" t="s">
+      <c r="B55" s="45"/>
+      <c r="C55" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="C53" s="44"/>
-      <c r="D53" s="44"/>
-      <c r="E53" s="44"/>
-      <c r="F53" s="44"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="43" t="s">
+      <c r="D55" s="46"/>
+      <c r="E55" s="46"/>
+      <c r="F55" s="46"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B54" s="44" t="s">
+      <c r="B56" s="45"/>
+      <c r="C56" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="C54" s="44"/>
-      <c r="D54" s="44"/>
-      <c r="E54" s="44"/>
-      <c r="F54" s="44"/>
+      <c r="D56" s="46"/>
+      <c r="E56" s="46"/>
+      <c r="F56" s="46"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="B57" s="45"/>
+      <c r="C57" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="D57" s="46"/>
+      <c r="E57" s="46"/>
+      <c r="F57" s="46"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="B58" s="45"/>
+      <c r="C58" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="D58" s="46"/>
+      <c r="E58" s="46"/>
+      <c r="F58" s="46"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="45" t="s">
+        <v>77</v>
+      </c>
+      <c r="B59" s="45"/>
+      <c r="C59" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="D59" s="46"/>
+      <c r="E59" s="46"/>
+      <c r="F59" s="46"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="B60" s="45"/>
+      <c r="C60" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="D60" s="46"/>
+      <c r="E60" s="46"/>
+      <c r="F60" s="46"/>
+    </row>
+    <row r="62" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B62" s="11"/>
+      <c r="C62" s="11"/>
+      <c r="D62" s="11"/>
+      <c r="E62" s="11"/>
+      <c r="F62" s="11"/>
+    </row>
+    <row r="63" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="47" t="s">
+        <v>84</v>
+      </c>
+      <c r="B64" s="47"/>
+      <c r="C64" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="D64" s="48"/>
+      <c r="E64" s="48"/>
+      <c r="F64" s="49">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="B65" s="50"/>
+      <c r="C65" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="D65" s="51"/>
+      <c r="E65" s="51"/>
+      <c r="F65" s="52">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="B66" s="47"/>
+      <c r="C66" s="48" t="s">
+        <v>89</v>
+      </c>
+      <c r="D66" s="48"/>
+      <c r="E66" s="48"/>
+      <c r="F66" s="49">
+        <v>19.6338</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="B67" s="50"/>
+      <c r="C67" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="D67" s="51"/>
+      <c r="E67" s="51"/>
+      <c r="F67" s="52">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B68" s="47"/>
+      <c r="C68" s="48" t="s">
+        <v>93</v>
+      </c>
+      <c r="D68" s="48"/>
+      <c r="E68" s="48"/>
+      <c r="F68" s="53">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="B69" s="50"/>
+      <c r="C69" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="D69" s="51"/>
+      <c r="E69" s="51"/>
+      <c r="F69" s="52">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="B70" s="47"/>
+      <c r="C70" s="48" t="s">
+        <v>96</v>
+      </c>
+      <c r="D70" s="48"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="54">
+        <v>348801</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B71" s="50"/>
+      <c r="C71" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="D71" s="51"/>
+      <c r="E71" s="51"/>
+      <c r="F71" s="55">
+        <v>4113.2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="B72" s="47"/>
+      <c r="C72" s="48" t="s">
+        <v>100</v>
+      </c>
+      <c r="D72" s="48"/>
+      <c r="E72" s="48"/>
+      <c r="F72" s="54">
+        <v>9880</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="B73" s="50"/>
+      <c r="C73" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="D73" s="51"/>
+      <c r="E73" s="51"/>
+      <c r="F73" s="55">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="47" t="s">
+        <v>102</v>
+      </c>
+      <c r="B74" s="47"/>
+      <c r="C74" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="D74" s="48"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="54">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="B75" s="50"/>
+      <c r="C75" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="D75" s="51"/>
+      <c r="E75" s="51"/>
+      <c r="F75" s="55">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="B76" s="47"/>
+      <c r="C76" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="D76" s="48"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="54">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="B77" s="50"/>
+      <c r="C77" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="D77" s="51"/>
+      <c r="E77" s="51"/>
+      <c r="F77" s="55">
+        <v>7053.52</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="B78" s="47"/>
+      <c r="C78" s="48" t="s">
+        <v>110</v>
+      </c>
+      <c r="D78" s="48"/>
+      <c r="E78" s="48"/>
+      <c r="F78" s="54">
+        <v>20240</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="B79" s="50"/>
+      <c r="C79" s="51" t="s">
+        <v>112</v>
+      </c>
+      <c r="D79" s="51"/>
+      <c r="E79" s="51"/>
+      <c r="F79" s="55">
+        <v>3160.521</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="56" t="s">
+        <v>113</v>
+      </c>
+      <c r="B80" s="56"/>
+      <c r="C80" s="57" t="s">
+        <v>114</v>
+      </c>
+      <c r="D80" s="57"/>
+      <c r="E80" s="57"/>
+      <c r="F80" s="58">
+        <v>403548.24100000004</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="B81" s="50"/>
+      <c r="C81" s="51" t="s">
+        <v>116</v>
+      </c>
+      <c r="D81" s="51"/>
+      <c r="E81" s="51"/>
+      <c r="F81" s="55">
+        <v>2509.992078683575</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="B82" s="47"/>
+      <c r="C82" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="D82" s="48"/>
+      <c r="E82" s="48"/>
+      <c r="F82" s="54">
+        <v>13086.075206340582</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="50" t="s">
+        <v>119</v>
+      </c>
+      <c r="B83" s="50"/>
+      <c r="C83" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="D83" s="51"/>
+      <c r="E83" s="51"/>
+      <c r="F83" s="55">
+        <v>68232.7943719807</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="47" t="s">
+        <v>121</v>
+      </c>
+      <c r="B84" s="47"/>
+      <c r="C84" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="D84" s="48"/>
+      <c r="E84" s="48"/>
+      <c r="F84" s="54">
+        <v>81318.86957832126</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="50" t="s">
+        <v>123</v>
+      </c>
+      <c r="B85" s="50"/>
+      <c r="C85" s="51" t="s">
+        <v>124</v>
+      </c>
+      <c r="D85" s="51"/>
+      <c r="E85" s="51"/>
+      <c r="F85" s="55">
+        <v>15760.207480964978</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="56" t="s">
+        <v>125</v>
+      </c>
+      <c r="B86" s="56"/>
+      <c r="C86" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="D86" s="57"/>
+      <c r="E86" s="57"/>
+      <c r="F86" s="58">
+        <v>503137.3101379699</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="56" t="s">
+        <v>127</v>
+      </c>
+      <c r="B87" s="56"/>
+      <c r="C87" s="57" t="s">
+        <v>128</v>
+      </c>
+      <c r="D87" s="57"/>
+      <c r="E87" s="57"/>
+      <c r="F87" s="58">
+        <v>421818.4405596487</v>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B89" s="11"/>
+      <c r="C89" s="11"/>
+      <c r="D89" s="11"/>
+      <c r="E89" s="11"/>
+      <c r="F89" s="11"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="45" t="s">
+        <v>130</v>
+      </c>
+      <c r="B90" s="45"/>
+      <c r="C90" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="D90" s="46"/>
+      <c r="E90" s="46"/>
+      <c r="F90" s="46"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="B91" s="45"/>
+      <c r="C91" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="D91" s="46"/>
+      <c r="E91" s="46"/>
+      <c r="F91" s="46"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="B92" s="45"/>
+      <c r="C92" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="D92" s="46"/>
+      <c r="E92" s="46"/>
+      <c r="F92" s="46"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="B93" s="45"/>
+      <c r="C93" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="D93" s="46"/>
+      <c r="E93" s="46"/>
+      <c r="F93" s="46"/>
+    </row>
+    <row r="95" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="B95" s="43"/>
+      <c r="C95" s="43"/>
+      <c r="D95" s="43"/>
+      <c r="E95" s="43"/>
+      <c r="F95" s="43"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="B96" s="44"/>
+      <c r="C96" s="44"/>
+      <c r="D96" s="44"/>
+      <c r="E96" s="44"/>
+      <c r="F96" s="44"/>
+    </row>
+    <row r="98" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="59" t="s">
+        <v>41</v>
+      </c>
+      <c r="B98" s="60" t="s">
+        <v>35</v>
+      </c>
+      <c r="C98" s="61" t="s">
+        <v>69</v>
+      </c>
+      <c r="D98" s="61"/>
+      <c r="E98" s="61"/>
+      <c r="F98" s="62" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="99" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="63" t="s">
+        <v>141</v>
+      </c>
+      <c r="B99" s="64">
+        <v>130</v>
+      </c>
+      <c r="C99" s="61" t="s">
+        <v>71</v>
+      </c>
+      <c r="D99" s="61"/>
+      <c r="E99" s="61"/>
+      <c r="F99" s="62" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="100" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="63" t="s">
+        <v>143</v>
+      </c>
+      <c r="B100" s="64">
+        <v>45</v>
+      </c>
+      <c r="C100" s="61" t="s">
+        <v>73</v>
+      </c>
+      <c r="D100" s="61"/>
+      <c r="E100" s="61"/>
+      <c r="F100" s="62" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="101" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="59" t="s">
+        <v>145</v>
+      </c>
+      <c r="B101" s="60" t="s">
+        <v>35</v>
+      </c>
+      <c r="C101" s="61" t="s">
+        <v>75</v>
+      </c>
+      <c r="D101" s="61"/>
+      <c r="E101" s="61"/>
+      <c r="F101" s="62" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="102" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="63" t="s">
+        <v>147</v>
+      </c>
+      <c r="B102" s="62" t="s">
+        <v>148</v>
+      </c>
+      <c r="C102" s="65" t="s">
+        <v>149</v>
+      </c>
+      <c r="D102" s="65"/>
+      <c r="E102" s="65"/>
+      <c r="F102" s="60" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="103" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="59" t="s">
+        <v>150</v>
+      </c>
+      <c r="B103" s="60" t="s">
+        <v>35</v>
+      </c>
+      <c r="C103" s="61" t="s">
+        <v>151</v>
+      </c>
+      <c r="D103" s="61"/>
+      <c r="E103" s="61"/>
+      <c r="F103" s="62" t="s">
+        <v>152</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="132">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A2:D2"/>
@@ -1992,629 +2571,99 @@
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="A48:C48"/>
     <mergeCell ref="A50:F50"/>
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="C55:F55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="C56:F56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="C57:F57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="C58:F58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="C59:F59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="C60:F60"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="C83:E83"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="C85:E85"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="C87:E87"/>
+    <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="C90:F90"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="C91:F91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:F92"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="C93:F93"/>
+    <mergeCell ref="A95:F95"/>
+    <mergeCell ref="A96:F96"/>
+    <mergeCell ref="C98:E98"/>
+    <mergeCell ref="C99:E99"/>
+    <mergeCell ref="C100:E100"/>
+    <mergeCell ref="C101:E101"/>
+    <mergeCell ref="C102:E102"/>
+    <mergeCell ref="C103:E103"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.25" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="80" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="78" fitToWidth="1" fitToHeight="1"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;8ul. Leśna 5, Wrocław&amp;R&amp;8Strona &amp;P z &amp;N</oddFooter>
   </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E47"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="5" width="19" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="43" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" s="44" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="43" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" s="44" t="s">
-        <v>79</v>
-      </c>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" s="44" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="B8" s="44" t="s">
-        <v>83</v>
-      </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="B9" s="44" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="43" t="s">
-        <v>86</v>
-      </c>
-      <c r="B10" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="43" t="s">
-        <v>88</v>
-      </c>
-      <c r="B11" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-    </row>
-    <row r="13" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-    </row>
-    <row r="14" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="B15" s="48" t="s">
-        <v>94</v>
-      </c>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="49">
-        <v>50.6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="50" t="s">
-        <v>95</v>
-      </c>
-      <c r="B16" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="52">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="47" t="s">
-        <v>97</v>
-      </c>
-      <c r="B17" s="48" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="49">
-        <v>19.6338</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="B18" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="52">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="47" t="s">
-        <v>101</v>
-      </c>
-      <c r="B19" s="48" t="s">
-        <v>102</v>
-      </c>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="53">
-        <v>3640</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="50" t="s">
-        <v>103</v>
-      </c>
-      <c r="B20" s="51" t="s">
-        <v>104</v>
-      </c>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="52">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="48" t="s">
-        <v>105</v>
-      </c>
-      <c r="C21" s="48"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="54">
-        <v>348801</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="B22" s="51" t="s">
-        <v>107</v>
-      </c>
-      <c r="C22" s="51"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="55">
-        <v>4113.2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="47" t="s">
-        <v>108</v>
-      </c>
-      <c r="B23" s="48" t="s">
-        <v>109</v>
-      </c>
-      <c r="C23" s="48"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="54">
-        <v>9880</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="51" t="s">
-        <v>110</v>
-      </c>
-      <c r="C24" s="51"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="55">
-        <v>3200</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="47" t="s">
-        <v>111</v>
-      </c>
-      <c r="B25" s="48" t="s">
-        <v>112</v>
-      </c>
-      <c r="C25" s="48"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="54">
-        <v>4800</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="50" t="s">
-        <v>113</v>
-      </c>
-      <c r="B26" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="C26" s="51"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="55">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="47" t="s">
-        <v>115</v>
-      </c>
-      <c r="B27" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="C27" s="48"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="54">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="50" t="s">
-        <v>117</v>
-      </c>
-      <c r="B28" s="51" t="s">
-        <v>118</v>
-      </c>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="55">
-        <v>7053.52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="47" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="48" t="s">
-        <v>119</v>
-      </c>
-      <c r="C29" s="48"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="54">
-        <v>20240</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="50" t="s">
-        <v>120</v>
-      </c>
-      <c r="B30" s="51" t="s">
-        <v>121</v>
-      </c>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="55">
-        <v>3160.521</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="56" t="s">
-        <v>122</v>
-      </c>
-      <c r="B31" s="57" t="s">
-        <v>123</v>
-      </c>
-      <c r="C31" s="57"/>
-      <c r="D31" s="57"/>
-      <c r="E31" s="58">
-        <v>403548.24100000004</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="50" t="s">
-        <v>124</v>
-      </c>
-      <c r="B32" s="51" t="s">
-        <v>125</v>
-      </c>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="55">
-        <v>2509.992078683575</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="47" t="s">
-        <v>126</v>
-      </c>
-      <c r="B33" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="C33" s="48"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="54">
-        <v>13086.075206340582</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="B34" s="51" t="s">
-        <v>129</v>
-      </c>
-      <c r="C34" s="51"/>
-      <c r="D34" s="51"/>
-      <c r="E34" s="55">
-        <v>68232.7943719807</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="47" t="s">
-        <v>130</v>
-      </c>
-      <c r="B35" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="54">
-        <v>81318.86957832126</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="50" t="s">
-        <v>132</v>
-      </c>
-      <c r="B36" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="55">
-        <v>15760.207480964978</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="56" t="s">
-        <v>134</v>
-      </c>
-      <c r="B37" s="57" t="s">
-        <v>135</v>
-      </c>
-      <c r="C37" s="57"/>
-      <c r="D37" s="57"/>
-      <c r="E37" s="58">
-        <v>503137.3101379699</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="56" t="s">
-        <v>136</v>
-      </c>
-      <c r="B38" s="57" t="s">
-        <v>137</v>
-      </c>
-      <c r="C38" s="57"/>
-      <c r="D38" s="57"/>
-      <c r="E38" s="58">
-        <v>421818.4405596487</v>
-      </c>
-    </row>
-    <row r="39" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="45" t="s">
-        <v>138</v>
-      </c>
-      <c r="B39" s="45"/>
-      <c r="C39" s="45"/>
-      <c r="D39" s="45"/>
-      <c r="E39" s="45"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="46" t="s">
-        <v>139</v>
-      </c>
-      <c r="B40" s="46"/>
-      <c r="C40" s="46"/>
-      <c r="D40" s="46"/>
-      <c r="E40" s="46"/>
-    </row>
-    <row r="42" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="59" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="60" t="s">
-        <v>35</v>
-      </c>
-      <c r="C42" s="61" t="s">
-        <v>78</v>
-      </c>
-      <c r="D42" s="61"/>
-      <c r="E42" s="62" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="43" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="61" t="s">
-        <v>141</v>
-      </c>
-      <c r="B43" s="63">
-        <v>130</v>
-      </c>
-      <c r="C43" s="61" t="s">
-        <v>80</v>
-      </c>
-      <c r="D43" s="61"/>
-      <c r="E43" s="62" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="44" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="61" t="s">
-        <v>143</v>
-      </c>
-      <c r="B44" s="63">
-        <v>45</v>
-      </c>
-      <c r="C44" s="61" t="s">
-        <v>82</v>
-      </c>
-      <c r="D44" s="61"/>
-      <c r="E44" s="62" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="45" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="59" t="s">
-        <v>145</v>
-      </c>
-      <c r="B45" s="60" t="s">
-        <v>35</v>
-      </c>
-      <c r="C45" s="61" t="s">
-        <v>84</v>
-      </c>
-      <c r="D45" s="61"/>
-      <c r="E45" s="62" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="46" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="61" t="s">
-        <v>147</v>
-      </c>
-      <c r="B46" s="62" t="s">
-        <v>148</v>
-      </c>
-      <c r="C46" s="59" t="s">
-        <v>149</v>
-      </c>
-      <c r="D46" s="59"/>
-      <c r="E46" s="60" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="47" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="59" t="s">
-        <v>150</v>
-      </c>
-      <c r="B47" s="60" t="s">
-        <v>35</v>
-      </c>
-      <c r="C47" s="61" t="s">
-        <v>151</v>
-      </c>
-      <c r="D47" s="61"/>
-      <c r="E47" s="62" t="s">
-        <v>152</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="44">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-  </mergeCells>
-  <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.25" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="82" fitToWidth="1" fitToHeight="1"/>
-  <headerFooter>
-    <oddFooter>&amp;L&amp;8ul. Leśna 5, Wrocław&amp;R&amp;8Strona &amp;P z &amp;N</oddFooter>
-  </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="38" max="16838" man="1"/>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="49" max="16838" man="1"/>
+    <brk id="94" max="16838" man="1"/>
   </rowBreaks>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
@@ -22,10 +22,10 @@
     <t>ul. Leśna 5, Wrocław</t>
   </si>
   <si>
-    <t>21.10.2026, 10:28</t>
-  </si>
-  <si>
-    <t>Wygenerowano 30.10.2026, 10:28:00 · ceny netto w zł · szablon NK41</t>
+    <t>21.10.2026, 11:44</t>
+  </si>
+  <si>
+    <t>Wygenerowano 30.10.2026, 11:44:46 · ceny netto w zł · szablon NK41</t>
   </si>
   <si>
     <t>Cena</t>
@@ -696,7 +696,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
@@ -882,7 +882,10 @@
       <alignment indent="1"/>
     </xf>
     <xf numFmtId="171" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="3"/>
@@ -2493,14 +2496,14 @@
       <c r="A102" s="63" t="s">
         <v>147</v>
       </c>
-      <c r="B102" s="62" t="s">
+      <c r="B102" s="65" t="s">
         <v>148</v>
       </c>
-      <c r="C102" s="65" t="s">
+      <c r="C102" s="66" t="s">
         <v>149</v>
       </c>
-      <c r="D102" s="65"/>
-      <c r="E102" s="65"/>
+      <c r="D102" s="66"/>
+      <c r="E102" s="66"/>
       <c r="F102" s="60" t="s">
         <v>35</v>
       </c>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
@@ -22,10 +22,10 @@
     <t>ul. Leśna 5, Wrocław</t>
   </si>
   <si>
-    <t>21.10.2026, 11:44</t>
-  </si>
-  <si>
-    <t>Wygenerowano 30.10.2026, 11:44:46 · ceny netto w zł · szablon NK41</t>
+    <t>21.10.2026, 12:42</t>
+  </si>
+  <si>
+    <t>Wygenerowano 30.10.2026, 12:42:34 · ceny netto w zł · szablon NK41</t>
   </si>
   <si>
     <t>Cena</t>

--- a/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
+++ b/kalkulator-nk38/przyklady/Kalkulator_ul_Lesna_5_Wroclaw_NK41.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="154">
   <si>
     <t>KALKULACJA NK41</t>
   </si>
@@ -22,10 +22,10 @@
     <t>ul. Leśna 5, Wrocław</t>
   </si>
   <si>
-    <t>21.10.2026, 12:42</t>
-  </si>
-  <si>
-    <t>Wygenerowano 30.10.2026, 12:42:34 · ceny netto w zł · szablon NK41</t>
+    <t>21.10.2026, 12:45</t>
+  </si>
+  <si>
+    <t>Ceny netto · wygenerowano 30.10.2026</t>
   </si>
   <si>
     <t>Cena</t>
@@ -40,7 +40,10 @@
     <t>Rabat od oferty</t>
   </si>
   <si>
-    <t>Cena ofertowa · zysk 14% · 2000 kg · 2529 € / MP</t>
+    <t>Cena ofertowa · zysk 14% · 2000 kg</t>
+  </si>
+  <si>
+    <t>10 938 zł · 2529 €</t>
   </si>
   <si>
     <t>–</t>
@@ -52,13 +55,13 @@
     <t>−19 415 zł (−3,86%)</t>
   </si>
   <si>
-    <t>Próg opłacalności · zysk 0% (maks. rabat)</t>
+    <t>Próg opłacalności · zysk 0% · maks. rabat</t>
   </si>
   <si>
     <t>−80 306 zł (−15,96%)</t>
   </si>
   <si>
-    <t>Pole do negocjacji: o ile można zejść z ceny (2000 kg)</t>
+    <t>Pole do negocjacji (2000 kg)</t>
   </si>
   <si>
     <t>Zysk</t>
@@ -486,7 +489,7 @@
     <numFmt numFmtId="170" formatCode="&quot;+&quot;#,##0 &quot;zł&quot;"/>
     <numFmt numFmtId="171" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -496,98 +499,104 @@
     </font>
     <font>
       <color rgb="FF6A7780"/>
-      <sz val="8"/>
-      <name val="Arial"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0E171C"/>
-      <sz val="16"/>
-      <name val="Arial"/>
+      <sz val="17.5"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0E171C"/>
-      <sz val="13"/>
-      <name val="Arial"/>
+      <sz val="14.5"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <color rgb="FF6A7780"/>
-      <sz val="9"/>
-      <name val="Arial"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0A6B74"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF0E171C"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0E171C"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0A6B74"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0A6B74"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF13794A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FFB42318"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF6A7780"/>
+      <sz val="9.5"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0A6B74"/>
       <sz val="9"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FF0E171C"/>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0E171C"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF0A6B74"/>
-      <sz val="11"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF0A6B74"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF13794A"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FFB42318"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FF6A7780"/>
-      <sz val="8.5"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF0A6B74"/>
-      <sz val="8"/>
-      <name val="Arial"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF0E171C"/>
-      <sz val="11"/>
-      <name val="Arial"/>
+      <sz val="11.5"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <color rgb="FF6A7780"/>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF6A7780"/>
-      <sz val="9"/>
-      <name val="Arial"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <color rgb="FF0E171C"/>
-      <sz val="8.5"/>
-      <name val="Arial"/>
+      <sz val="9.5"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="9">
@@ -633,7 +642,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -666,12 +675,40 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFD3D9DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD3D9DD"/>
+      </right>
       <top style="thin">
         <color rgb="FFD3D9DD"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD3D9DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD3D9DD"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD3D9DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD3D9DD"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD3D9DD"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -696,7 +733,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
@@ -784,21 +821,24 @@
       <alignment wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment indent="1"/>
+      <alignment vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -828,7 +868,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -864,30 +904,30 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="171" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="18" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="3"/>
     </xf>
   </cellXfs>
@@ -1229,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1299,16 +1339,16 @@
       <c r="D6" s="9">
         <v>503137.3101379699</v>
       </c>
-      <c r="E6" s="9">
-        <v>10937.767611694999</v>
+      <c r="E6" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -1319,12 +1359,12 @@
         <v>10515.710376868326</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -1335,12 +1375,12 @@
         <v>9191.985413093762</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -1350,7 +1390,7 @@
     </row>
     <row r="11" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>6</v>
@@ -1359,10 +1399,10 @@
         <v>8</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F11" s="13" t="s">
         <v>7</v>
@@ -1550,7 +1590,7 @@
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="29"/>
       <c r="C21" s="29"/>
@@ -1560,7 +1600,7 @@
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -1570,119 +1610,117 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24" s="30"/>
       <c r="C24" s="30"/>
       <c r="D24" s="30" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E24" s="30"/>
       <c r="F24" s="30"/>
     </row>
     <row r="25" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E25" s="31"/>
       <c r="F25" s="31"/>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E26" s="33"/>
       <c r="F26" s="33"/>
     </row>
     <row r="27" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B27" s="31"/>
       <c r="C27" s="31"/>
       <c r="D27" s="31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E27" s="31"/>
       <c r="F27" s="31"/>
     </row>
     <row r="28" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B28" s="33"/>
       <c r="C28" s="33"/>
       <c r="D28" s="33" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E28" s="33"/>
       <c r="F28" s="33"/>
     </row>
     <row r="29" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" s="31"/>
       <c r="C29" s="31"/>
       <c r="D29" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E29" s="31"/>
       <c r="F29" s="31"/>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B30" s="33"/>
       <c r="C30" s="33"/>
       <c r="D30" s="33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E30" s="33"/>
       <c r="F30" s="33"/>
     </row>
     <row r="31" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="31" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B31" s="31"/>
       <c r="C31" s="31"/>
       <c r="D31" s="31" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E31" s="31"/>
       <c r="F31" s="31"/>
     </row>
     <row r="32" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" s="33"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
+      <c r="A32" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="34"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" s="35" t="s">
+      <c r="A34" s="35" t="s">
         <v>39</v>
       </c>
+      <c r="B34" s="35"/>
       <c r="C34" s="35"/>
       <c r="D34" s="35"/>
       <c r="E34" s="35"/>
@@ -1693,171 +1731,165 @@
         <v>40</v>
       </c>
       <c r="B35" s="36"/>
-      <c r="C35" s="36" t="s">
+      <c r="C35" s="36"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="36"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="37" t="s">
         <v>41</v>
-      </c>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="F35" s="36"/>
-    </row>
-    <row r="36" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="37" t="s">
-        <v>43</v>
       </c>
       <c r="B36" s="37"/>
       <c r="C36" s="37" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D36" s="37"/>
       <c r="E36" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="F36" s="37"/>
+    </row>
+    <row r="37" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="38"/>
+      <c r="C37" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="F36" s="37"/>
-    </row>
-    <row r="38" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
+      <c r="D37" s="38"/>
+      <c r="E37" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="F37" s="38"/>
+    </row>
+    <row r="39" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="13" t="s">
+      <c r="B39" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="F38" s="13" t="s">
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="13" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="38" t="s">
+      <c r="F39" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="B39" s="39" t="s">
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="C39" s="39"/>
-      <c r="D39" s="39"/>
-      <c r="E39" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" s="40" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="38" t="s">
+      <c r="B40" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="B40" s="39" t="s">
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="39"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="40">
+      <c r="B41" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="40"/>
+      <c r="D41" s="40"/>
+      <c r="E41" s="41">
         <v>113498.94718522218</v>
       </c>
-      <c r="F40" s="40">
+      <c r="F41" s="41">
         <v>109131.3879130116</v>
       </c>
     </row>
-    <row r="42" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="13" t="s">
+    <row r="43" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E42" s="13" t="s">
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="F42" s="13" t="s">
+      <c r="E43" s="13" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="8" t="s">
+      <c r="F43" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="41">
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="42">
         <v>805</v>
       </c>
-      <c r="E43" s="41">
+      <c r="E44" s="42">
         <v>9660</v>
       </c>
-      <c r="F43" s="41">
+      <c r="F44" s="42">
         <v>4830</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="42" t="s">
-        <v>59</v>
-      </c>
-      <c r="B44" s="42"/>
-      <c r="C44" s="42"/>
-      <c r="D44" s="9">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="43" t="s">
+        <v>60</v>
+      </c>
+      <c r="B45" s="43"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="9">
         <v>920</v>
       </c>
-      <c r="E44" s="9">
+      <c r="E45" s="9">
         <v>11040</v>
       </c>
-      <c r="F44" s="9">
+      <c r="F45" s="9">
         <v>5520</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="41">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="42">
         <v>1035</v>
       </c>
-      <c r="E45" s="41">
+      <c r="E46" s="42">
         <v>12420</v>
       </c>
-      <c r="F45" s="41">
+      <c r="F46" s="42">
         <v>6210</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="B46" s="42"/>
-      <c r="C46" s="42"/>
-      <c r="D46" s="9">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="B47" s="43"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="9">
         <v>1150</v>
       </c>
-      <c r="E46" s="9">
+      <c r="E47" s="9">
         <v>13800</v>
       </c>
-      <c r="F46" s="9">
+      <c r="F47" s="9">
         <v>6900</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="41">
-        <v>1265</v>
-      </c>
-      <c r="E47" s="41">
-        <v>15180</v>
-      </c>
-      <c r="F47" s="41">
-        <v>7590</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1866,27 +1898,33 @@
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
-      <c r="D48" s="41">
+      <c r="D48" s="42">
+        <v>1265</v>
+      </c>
+      <c r="E48" s="42">
+        <v>15180</v>
+      </c>
+      <c r="F48" s="42">
+        <v>7590</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="42">
         <v>1380</v>
       </c>
-      <c r="E48" s="41">
+      <c r="E49" s="42">
         <v>16560</v>
       </c>
-      <c r="F48" s="41">
+      <c r="F49" s="42">
         <v>8280</v>
       </c>
     </row>
-    <row r="50" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="B50" s="43"/>
-      <c r="C50" s="43"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="43"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="44" t="s">
         <v>65</v>
       </c>
@@ -1896,529 +1934,529 @@
       <c r="E51" s="44"/>
       <c r="F51" s="44"/>
     </row>
-    <row r="53" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="11" t="s">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="11"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="45" t="s">
+      <c r="B52" s="45"/>
+      <c r="C52" s="45"/>
+      <c r="D52" s="45"/>
+      <c r="E52" s="45"/>
+      <c r="F52" s="45"/>
+    </row>
+    <row r="54" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="B54" s="45"/>
-      <c r="C54" s="46" t="s">
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="D54" s="46"/>
-      <c r="E54" s="46"/>
-      <c r="F54" s="46"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="45" t="s">
+      <c r="B55" s="46"/>
+      <c r="C55" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="B55" s="45"/>
-      <c r="C55" s="46" t="s">
+      <c r="D55" s="47"/>
+      <c r="E55" s="47"/>
+      <c r="F55" s="47"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="D55" s="46"/>
-      <c r="E55" s="46"/>
-      <c r="F55" s="46"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="45" t="s">
+      <c r="B56" s="46"/>
+      <c r="C56" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="B56" s="45"/>
-      <c r="C56" s="46" t="s">
+      <c r="D56" s="47"/>
+      <c r="E56" s="47"/>
+      <c r="F56" s="47"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="D56" s="46"/>
-      <c r="E56" s="46"/>
-      <c r="F56" s="46"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="45" t="s">
+      <c r="B57" s="46"/>
+      <c r="C57" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="B57" s="45"/>
-      <c r="C57" s="46" t="s">
+      <c r="D57" s="47"/>
+      <c r="E57" s="47"/>
+      <c r="F57" s="47"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="D57" s="46"/>
-      <c r="E57" s="46"/>
-      <c r="F57" s="46"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="45" t="s">
+      <c r="B58" s="46"/>
+      <c r="C58" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="B58" s="45"/>
-      <c r="C58" s="46" t="s">
+      <c r="D58" s="47"/>
+      <c r="E58" s="47"/>
+      <c r="F58" s="47"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="D58" s="46"/>
-      <c r="E58" s="46"/>
-      <c r="F58" s="46"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="45" t="s">
+      <c r="B59" s="46"/>
+      <c r="C59" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="B59" s="45"/>
-      <c r="C59" s="46" t="s">
+      <c r="D59" s="47"/>
+      <c r="E59" s="47"/>
+      <c r="F59" s="47"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="D59" s="46"/>
-      <c r="E59" s="46"/>
-      <c r="F59" s="46"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="45" t="s">
+      <c r="B60" s="46"/>
+      <c r="C60" s="47" t="s">
         <v>79</v>
       </c>
-      <c r="B60" s="45"/>
-      <c r="C60" s="46" t="s">
-        <v>78</v>
-      </c>
-      <c r="D60" s="46"/>
-      <c r="E60" s="46"/>
-      <c r="F60" s="46"/>
-    </row>
-    <row r="62" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="11" t="s">
+      <c r="D60" s="47"/>
+      <c r="E60" s="47"/>
+      <c r="F60" s="47"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="B62" s="11"/>
-      <c r="C62" s="11"/>
-      <c r="D62" s="11"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="11"/>
-    </row>
-    <row r="63" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="6" t="s">
+      <c r="B61" s="46"/>
+      <c r="C61" s="47" t="s">
+        <v>79</v>
+      </c>
+      <c r="D61" s="47"/>
+      <c r="E61" s="47"/>
+      <c r="F61" s="47"/>
+    </row>
+    <row r="63" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="B63" s="6"/>
-      <c r="C63" s="6" t="s">
+      <c r="B63" s="11"/>
+      <c r="C63" s="11"/>
+      <c r="D63" s="11"/>
+      <c r="E63" s="11"/>
+      <c r="F63" s="11"/>
+    </row>
+    <row r="64" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="7" t="s">
+      <c r="B64" s="6"/>
+      <c r="C64" s="6" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="47" t="s">
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="B64" s="47"/>
-      <c r="C64" s="48" t="s">
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="48" t="s">
         <v>85</v>
       </c>
-      <c r="D64" s="48"/>
-      <c r="E64" s="48"/>
-      <c r="F64" s="49">
+      <c r="B65" s="48"/>
+      <c r="C65" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="D65" s="49"/>
+      <c r="E65" s="49"/>
+      <c r="F65" s="50">
         <v>50.6</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="B65" s="50"/>
-      <c r="C65" s="51" t="s">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="D65" s="51"/>
-      <c r="E65" s="51"/>
-      <c r="F65" s="52">
+      <c r="B66" s="51"/>
+      <c r="C66" s="52" t="s">
+        <v>88</v>
+      </c>
+      <c r="D66" s="52"/>
+      <c r="E66" s="52"/>
+      <c r="F66" s="53">
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="B66" s="47"/>
-      <c r="C66" s="48" t="s">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="D66" s="48"/>
-      <c r="E66" s="48"/>
-      <c r="F66" s="49">
+      <c r="B67" s="48"/>
+      <c r="C67" s="49" t="s">
+        <v>90</v>
+      </c>
+      <c r="D67" s="49"/>
+      <c r="E67" s="49"/>
+      <c r="F67" s="50">
         <v>19.6338</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="50" t="s">
-        <v>90</v>
-      </c>
-      <c r="B67" s="50"/>
-      <c r="C67" s="51" t="s">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="51" t="s">
         <v>91</v>
       </c>
-      <c r="D67" s="51"/>
-      <c r="E67" s="51"/>
-      <c r="F67" s="52">
+      <c r="B68" s="51"/>
+      <c r="C68" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="D68" s="52"/>
+      <c r="E68" s="52"/>
+      <c r="F68" s="53">
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="47" t="s">
-        <v>92</v>
-      </c>
-      <c r="B68" s="47"/>
-      <c r="C68" s="48" t="s">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="48" t="s">
         <v>93</v>
       </c>
-      <c r="D68" s="48"/>
-      <c r="E68" s="48"/>
-      <c r="F68" s="53">
+      <c r="B69" s="48"/>
+      <c r="C69" s="49" t="s">
+        <v>94</v>
+      </c>
+      <c r="D69" s="49"/>
+      <c r="E69" s="49"/>
+      <c r="F69" s="54">
         <v>3640</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="B69" s="50"/>
-      <c r="C69" s="51" t="s">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="D69" s="51"/>
-      <c r="E69" s="51"/>
-      <c r="F69" s="52">
+      <c r="B70" s="51"/>
+      <c r="C70" s="52" t="s">
+        <v>96</v>
+      </c>
+      <c r="D70" s="52"/>
+      <c r="E70" s="52"/>
+      <c r="F70" s="53">
         <v>76</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="B70" s="47"/>
-      <c r="C70" s="48" t="s">
-        <v>96</v>
-      </c>
-      <c r="D70" s="48"/>
-      <c r="E70" s="48"/>
-      <c r="F70" s="54">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="B71" s="48"/>
+      <c r="C71" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="D71" s="49"/>
+      <c r="E71" s="49"/>
+      <c r="F71" s="55">
         <v>348801</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="50" t="s">
-        <v>97</v>
-      </c>
-      <c r="B71" s="50"/>
-      <c r="C71" s="51" t="s">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="D71" s="51"/>
-      <c r="E71" s="51"/>
-      <c r="F71" s="55">
+      <c r="B72" s="51"/>
+      <c r="C72" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="D72" s="52"/>
+      <c r="E72" s="52"/>
+      <c r="F72" s="56">
         <v>4113.2</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="B72" s="47"/>
-      <c r="C72" s="48" t="s">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="D72" s="48"/>
-      <c r="E72" s="48"/>
-      <c r="F72" s="54">
+      <c r="B73" s="48"/>
+      <c r="C73" s="49" t="s">
+        <v>101</v>
+      </c>
+      <c r="D73" s="49"/>
+      <c r="E73" s="49"/>
+      <c r="F73" s="55">
         <v>9880</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="50" t="s">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="B74" s="51"/>
+      <c r="C74" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="D74" s="52"/>
+      <c r="E74" s="52"/>
+      <c r="F74" s="56">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="B75" s="48"/>
+      <c r="C75" s="49" t="s">
+        <v>104</v>
+      </c>
+      <c r="D75" s="49"/>
+      <c r="E75" s="49"/>
+      <c r="F75" s="55">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="B76" s="51"/>
+      <c r="C76" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="D76" s="52"/>
+      <c r="E76" s="52"/>
+      <c r="F76" s="56">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="B77" s="48"/>
+      <c r="C77" s="49" t="s">
+        <v>108</v>
+      </c>
+      <c r="D77" s="49"/>
+      <c r="E77" s="49"/>
+      <c r="F77" s="55">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="B78" s="51"/>
+      <c r="C78" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="D78" s="52"/>
+      <c r="E78" s="52"/>
+      <c r="F78" s="56">
+        <v>7053.52</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="B73" s="50"/>
-      <c r="C73" s="51" t="s">
-        <v>101</v>
-      </c>
-      <c r="D73" s="51"/>
-      <c r="E73" s="51"/>
-      <c r="F73" s="55">
-        <v>3200</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="47" t="s">
-        <v>102</v>
-      </c>
-      <c r="B74" s="47"/>
-      <c r="C74" s="48" t="s">
-        <v>103</v>
-      </c>
-      <c r="D74" s="48"/>
-      <c r="E74" s="48"/>
-      <c r="F74" s="54">
-        <v>4800</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="50" t="s">
-        <v>104</v>
-      </c>
-      <c r="B75" s="50"/>
-      <c r="C75" s="51" t="s">
-        <v>105</v>
-      </c>
-      <c r="D75" s="51"/>
-      <c r="E75" s="51"/>
-      <c r="F75" s="55">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="47" t="s">
-        <v>106</v>
-      </c>
-      <c r="B76" s="47"/>
-      <c r="C76" s="48" t="s">
-        <v>107</v>
-      </c>
-      <c r="D76" s="48"/>
-      <c r="E76" s="48"/>
-      <c r="F76" s="54">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="50" t="s">
-        <v>108</v>
-      </c>
-      <c r="B77" s="50"/>
-      <c r="C77" s="51" t="s">
-        <v>109</v>
-      </c>
-      <c r="D77" s="51"/>
-      <c r="E77" s="51"/>
-      <c r="F77" s="55">
-        <v>7053.52</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="47" t="s">
-        <v>41</v>
-      </c>
-      <c r="B78" s="47"/>
-      <c r="C78" s="48" t="s">
-        <v>110</v>
-      </c>
-      <c r="D78" s="48"/>
-      <c r="E78" s="48"/>
-      <c r="F78" s="54">
+      <c r="B79" s="48"/>
+      <c r="C79" s="49" t="s">
+        <v>111</v>
+      </c>
+      <c r="D79" s="49"/>
+      <c r="E79" s="49"/>
+      <c r="F79" s="55">
         <v>20240</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="50" t="s">
-        <v>111</v>
-      </c>
-      <c r="B79" s="50"/>
-      <c r="C79" s="51" t="s">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="51" t="s">
         <v>112</v>
       </c>
-      <c r="D79" s="51"/>
-      <c r="E79" s="51"/>
-      <c r="F79" s="55">
+      <c r="B80" s="51"/>
+      <c r="C80" s="52" t="s">
+        <v>113</v>
+      </c>
+      <c r="D80" s="52"/>
+      <c r="E80" s="52"/>
+      <c r="F80" s="56">
         <v>3160.521</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="56" t="s">
-        <v>113</v>
-      </c>
-      <c r="B80" s="56"/>
-      <c r="C80" s="57" t="s">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="57" t="s">
         <v>114</v>
       </c>
-      <c r="D80" s="57"/>
-      <c r="E80" s="57"/>
-      <c r="F80" s="58">
+      <c r="B81" s="57"/>
+      <c r="C81" s="58" t="s">
+        <v>115</v>
+      </c>
+      <c r="D81" s="58"/>
+      <c r="E81" s="58"/>
+      <c r="F81" s="59">
         <v>403548.24100000004</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="50" t="s">
-        <v>115</v>
-      </c>
-      <c r="B81" s="50"/>
-      <c r="C81" s="51" t="s">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="D81" s="51"/>
-      <c r="E81" s="51"/>
-      <c r="F81" s="55">
+      <c r="B82" s="51"/>
+      <c r="C82" s="52" t="s">
+        <v>117</v>
+      </c>
+      <c r="D82" s="52"/>
+      <c r="E82" s="52"/>
+      <c r="F82" s="56">
         <v>2509.992078683575</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="47" t="s">
-        <v>117</v>
-      </c>
-      <c r="B82" s="47"/>
-      <c r="C82" s="48" t="s">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="48" t="s">
         <v>118</v>
       </c>
-      <c r="D82" s="48"/>
-      <c r="E82" s="48"/>
-      <c r="F82" s="54">
+      <c r="B83" s="48"/>
+      <c r="C83" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="D83" s="49"/>
+      <c r="E83" s="49"/>
+      <c r="F83" s="55">
         <v>13086.075206340582</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="50" t="s">
-        <v>119</v>
-      </c>
-      <c r="B83" s="50"/>
-      <c r="C83" s="51" t="s">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="51" t="s">
         <v>120</v>
       </c>
-      <c r="D83" s="51"/>
-      <c r="E83" s="51"/>
-      <c r="F83" s="55">
+      <c r="B84" s="51"/>
+      <c r="C84" s="52" t="s">
+        <v>121</v>
+      </c>
+      <c r="D84" s="52"/>
+      <c r="E84" s="52"/>
+      <c r="F84" s="56">
         <v>68232.7943719807</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="B84" s="47"/>
-      <c r="C84" s="48" t="s">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="48" t="s">
         <v>122</v>
       </c>
-      <c r="D84" s="48"/>
-      <c r="E84" s="48"/>
-      <c r="F84" s="54">
+      <c r="B85" s="48"/>
+      <c r="C85" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="D85" s="49"/>
+      <c r="E85" s="49"/>
+      <c r="F85" s="55">
         <v>81318.86957832126</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="50" t="s">
-        <v>123</v>
-      </c>
-      <c r="B85" s="50"/>
-      <c r="C85" s="51" t="s">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="51" t="s">
         <v>124</v>
       </c>
-      <c r="D85" s="51"/>
-      <c r="E85" s="51"/>
-      <c r="F85" s="55">
+      <c r="B86" s="51"/>
+      <c r="C86" s="52" t="s">
+        <v>125</v>
+      </c>
+      <c r="D86" s="52"/>
+      <c r="E86" s="52"/>
+      <c r="F86" s="56">
         <v>15760.207480964978</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="56" t="s">
-        <v>125</v>
-      </c>
-      <c r="B86" s="56"/>
-      <c r="C86" s="57" t="s">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="57" t="s">
         <v>126</v>
       </c>
-      <c r="D86" s="57"/>
-      <c r="E86" s="57"/>
-      <c r="F86" s="58">
+      <c r="B87" s="57"/>
+      <c r="C87" s="58" t="s">
+        <v>127</v>
+      </c>
+      <c r="D87" s="58"/>
+      <c r="E87" s="58"/>
+      <c r="F87" s="59">
         <v>503137.3101379699</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="56" t="s">
-        <v>127</v>
-      </c>
-      <c r="B87" s="56"/>
-      <c r="C87" s="57" t="s">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="D87" s="57"/>
-      <c r="E87" s="57"/>
-      <c r="F87" s="58">
+      <c r="B88" s="57"/>
+      <c r="C88" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="D88" s="58"/>
+      <c r="E88" s="58"/>
+      <c r="F88" s="59">
         <v>421818.4405596487</v>
       </c>
     </row>
-    <row r="89" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="B89" s="11"/>
-      <c r="C89" s="11"/>
-      <c r="D89" s="11"/>
-      <c r="E89" s="11"/>
-      <c r="F89" s="11"/>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="45" t="s">
+    <row r="90" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="B90" s="45"/>
-      <c r="C90" s="46" t="s">
+      <c r="B90" s="11"/>
+      <c r="C90" s="11"/>
+      <c r="D90" s="11"/>
+      <c r="E90" s="11"/>
+      <c r="F90" s="11"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="D90" s="46"/>
-      <c r="E90" s="46"/>
-      <c r="F90" s="46"/>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="45" t="s">
+      <c r="B91" s="46"/>
+      <c r="C91" s="47" t="s">
         <v>132</v>
       </c>
-      <c r="B91" s="45"/>
-      <c r="C91" s="46" t="s">
+      <c r="D91" s="47"/>
+      <c r="E91" s="47"/>
+      <c r="F91" s="47"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="D91" s="46"/>
-      <c r="E91" s="46"/>
-      <c r="F91" s="46"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="45" t="s">
+      <c r="B92" s="46"/>
+      <c r="C92" s="47" t="s">
         <v>134</v>
       </c>
-      <c r="B92" s="45"/>
-      <c r="C92" s="46" t="s">
+      <c r="D92" s="47"/>
+      <c r="E92" s="47"/>
+      <c r="F92" s="47"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="46" t="s">
         <v>135</v>
       </c>
-      <c r="D92" s="46"/>
-      <c r="E92" s="46"/>
-      <c r="F92" s="46"/>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="45" t="s">
+      <c r="B93" s="46"/>
+      <c r="C93" s="47" t="s">
         <v>136</v>
       </c>
-      <c r="B93" s="45"/>
-      <c r="C93" s="46" t="s">
+      <c r="D93" s="47"/>
+      <c r="E93" s="47"/>
+      <c r="F93" s="47"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="46" t="s">
         <v>137</v>
       </c>
-      <c r="D93" s="46"/>
-      <c r="E93" s="46"/>
-      <c r="F93" s="46"/>
-    </row>
-    <row r="95" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="43" t="s">
+      <c r="B94" s="46"/>
+      <c r="C94" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="B95" s="43"/>
-      <c r="C95" s="43"/>
-      <c r="D95" s="43"/>
-      <c r="E95" s="43"/>
-      <c r="F95" s="43"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D94" s="47"/>
+      <c r="E94" s="47"/>
+      <c r="F94" s="47"/>
+    </row>
+    <row r="96" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="44" t="s">
         <v>139</v>
       </c>
@@ -2428,104 +2466,114 @@
       <c r="E96" s="44"/>
       <c r="F96" s="44"/>
     </row>
-    <row r="98" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="59" t="s">
-        <v>41</v>
-      </c>
-      <c r="B98" s="60" t="s">
-        <v>35</v>
-      </c>
-      <c r="C98" s="61" t="s">
-        <v>69</v>
-      </c>
-      <c r="D98" s="61"/>
-      <c r="E98" s="61"/>
-      <c r="F98" s="62" t="s">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="45" t="s">
         <v>140</v>
       </c>
+      <c r="B97" s="45"/>
+      <c r="C97" s="45"/>
+      <c r="D97" s="45"/>
+      <c r="E97" s="45"/>
+      <c r="F97" s="45"/>
     </row>
     <row r="99" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="63" t="s">
+      <c r="A99" s="60" t="s">
+        <v>42</v>
+      </c>
+      <c r="B99" s="61" t="s">
+        <v>36</v>
+      </c>
+      <c r="C99" s="62" t="s">
+        <v>70</v>
+      </c>
+      <c r="D99" s="62"/>
+      <c r="E99" s="62"/>
+      <c r="F99" s="63" t="s">
         <v>141</v>
       </c>
-      <c r="B99" s="64">
+    </row>
+    <row r="100" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="64" t="s">
+        <v>142</v>
+      </c>
+      <c r="B100" s="65">
         <v>130</v>
       </c>
-      <c r="C99" s="61" t="s">
-        <v>71</v>
-      </c>
-      <c r="D99" s="61"/>
-      <c r="E99" s="61"/>
-      <c r="F99" s="62" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="100" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="63" t="s">
+      <c r="C100" s="62" t="s">
+        <v>72</v>
+      </c>
+      <c r="D100" s="62"/>
+      <c r="E100" s="62"/>
+      <c r="F100" s="63" t="s">
         <v>143</v>
       </c>
-      <c r="B100" s="64">
+    </row>
+    <row r="101" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="64" t="s">
+        <v>144</v>
+      </c>
+      <c r="B101" s="65">
         <v>45</v>
       </c>
-      <c r="C100" s="61" t="s">
-        <v>73</v>
-      </c>
-      <c r="D100" s="61"/>
-      <c r="E100" s="61"/>
-      <c r="F100" s="62" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="101" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" s="59" t="s">
+      <c r="C101" s="62" t="s">
+        <v>74</v>
+      </c>
+      <c r="D101" s="62"/>
+      <c r="E101" s="62"/>
+      <c r="F101" s="63" t="s">
         <v>145</v>
       </c>
-      <c r="B101" s="60" t="s">
-        <v>35</v>
-      </c>
-      <c r="C101" s="61" t="s">
-        <v>75</v>
-      </c>
-      <c r="D101" s="61"/>
-      <c r="E101" s="61"/>
-      <c r="F101" s="62" t="s">
+    </row>
+    <row r="102" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="60" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="102" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" s="63" t="s">
+      <c r="B102" s="61" t="s">
+        <v>36</v>
+      </c>
+      <c r="C102" s="62" t="s">
+        <v>76</v>
+      </c>
+      <c r="D102" s="62"/>
+      <c r="E102" s="62"/>
+      <c r="F102" s="63" t="s">
         <v>147</v>
       </c>
-      <c r="B102" s="65" t="s">
+    </row>
+    <row r="103" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="64" t="s">
         <v>148</v>
       </c>
-      <c r="C102" s="66" t="s">
+      <c r="B103" s="66" t="s">
         <v>149</v>
       </c>
-      <c r="D102" s="66"/>
-      <c r="E102" s="66"/>
-      <c r="F102" s="60" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="103" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="59" t="s">
+      <c r="C103" s="67" t="s">
         <v>150</v>
       </c>
-      <c r="B103" s="60" t="s">
-        <v>35</v>
-      </c>
-      <c r="C103" s="61" t="s">
+      <c r="D103" s="67"/>
+      <c r="E103" s="67"/>
+      <c r="F103" s="61" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="104" ht="13" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="60" t="s">
         <v>151</v>
       </c>
-      <c r="D103" s="61"/>
-      <c r="E103" s="61"/>
-      <c r="F103" s="62" t="s">
+      <c r="B104" s="61" t="s">
+        <v>36</v>
+      </c>
+      <c r="C104" s="62" t="s">
         <v>152</v>
       </c>
+      <c r="D104" s="62"/>
+      <c r="E104" s="62"/>
+      <c r="F104" s="63" t="s">
+        <v>153</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="132">
+  <mergeCells count="133">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A2:D2"/>
@@ -2556,28 +2604,27 @@
     <mergeCell ref="D31:F31"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="D32:F32"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:F35"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="E36:F36"/>
-    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="E37:F37"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="B40:D40"/>
-    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="B41:D41"/>
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A49:C49"/>
     <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A53:F53"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A54:F54"/>
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="C55:F55"/>
     <mergeCell ref="A56:B56"/>
@@ -2590,9 +2637,9 @@
     <mergeCell ref="C59:F59"/>
     <mergeCell ref="A60:B60"/>
     <mergeCell ref="C60:F60"/>
-    <mergeCell ref="A62:F62"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="C61:F61"/>
+    <mergeCell ref="A63:F63"/>
     <mergeCell ref="A64:B64"/>
     <mergeCell ref="C64:E64"/>
     <mergeCell ref="A65:B65"/>
@@ -2641,32 +2688,34 @@
     <mergeCell ref="C86:E86"/>
     <mergeCell ref="A87:B87"/>
     <mergeCell ref="C87:E87"/>
-    <mergeCell ref="A89:F89"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="C90:F90"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="C88:E88"/>
+    <mergeCell ref="A90:F90"/>
     <mergeCell ref="A91:B91"/>
     <mergeCell ref="C91:F91"/>
     <mergeCell ref="A92:B92"/>
     <mergeCell ref="C92:F92"/>
     <mergeCell ref="A93:B93"/>
     <mergeCell ref="C93:F93"/>
-    <mergeCell ref="A95:F95"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:F94"/>
     <mergeCell ref="A96:F96"/>
-    <mergeCell ref="C98:E98"/>
+    <mergeCell ref="A97:F97"/>
     <mergeCell ref="C99:E99"/>
     <mergeCell ref="C100:E100"/>
     <mergeCell ref="C101:E101"/>
     <mergeCell ref="C102:E102"/>
     <mergeCell ref="C103:E103"/>
+    <mergeCell ref="C104:E104"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.25" footer="0.25"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="78" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="82" fitToWidth="1" fitToHeight="1"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;8ul. Leśna 5, Wrocław&amp;R&amp;8Strona &amp;P z &amp;N</oddFooter>
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="49" max="16838" man="1"/>
-    <brk id="94" max="16838" man="1"/>
+    <brk id="50" max="16838" man="1"/>
+    <brk id="95" max="16838" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>